--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -67,37 +67,37 @@
     <t>sale</t>
   </si>
   <si>
-    <t>手工1，下回合获得你手工的牌</t>
-  </si>
-  <si>
-    <t>美化4</t>
-  </si>
-  <si>
-    <t>拆卸1，下回合随机获得一个罕见礼物</t>
-  </si>
-  <si>
-    <t>拆卸1，仙台同学的属性二提升30点</t>
-  </si>
-  <si>
-    <t>拆卸2，属性一提升50点</t>
-  </si>
-  <si>
-    <t>美化，将卡中数值不足12的部分加成到12</t>
-  </si>
-  <si>
-    <t>手工3，下回合获得你手工的牌</t>
-  </si>
-  <si>
-    <t>手工1，下回合随机获得一个普通礼物</t>
+    <t>生枝1，下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>生长4</t>
+  </si>
+  <si>
+    <t>剪枝1，下回合随机获得一个罕见礼物</t>
+  </si>
+  <si>
+    <t>剪枝1，仙台同学的防御属性提升30点</t>
+  </si>
+  <si>
+    <t>剪枝2，攻击属性提升50点</t>
+  </si>
+  <si>
+    <t>生长，将卡中数值不足12的部分加成到12</t>
+  </si>
+  <si>
+    <t>生枝3，下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>生枝1，下回合随机获得一个普通礼物</t>
   </si>
   <si>
     <t>大破坏</t>
   </si>
   <si>
-    <t>拆卸5，仙台同学的属性一，三提升100点</t>
-  </si>
-  <si>
-    <t>若卡组中有三个以上相同的礼物，美化40，否则美化5</t>
+    <t>剪枝5，仙台同学的攻击属性，三提升100点</t>
+  </si>
+  <si>
+    <t>若卡组中有三个以上相同的礼物，生长40，否则生长5</t>
   </si>
   <si>
     <t>凭空</t>
@@ -106,16 +106,16 @@
     <t>若手中没有礼物牌，则随机获得一个罕见礼物卡</t>
   </si>
   <si>
-    <t>美化4，此牌美化的数值提升4</t>
-  </si>
-  <si>
-    <t>拆卸1，若此礼物包含属性一的加成，提升属性二40点</t>
+    <t>生长4，此牌生长的数值提升4</t>
+  </si>
+  <si>
+    <t>剪枝1，若此礼物包含攻击属性的加成，提升防御属性40点</t>
   </si>
   <si>
     <t>将手牌中的所有礼物都变成同一个随机礼物</t>
   </si>
   <si>
-    <t>若卡组中有6个以上相同的礼物，美化所有相同的礼物80</t>
+    <t>若卡组中有6个以上相同的礼物，生长所有相同的礼物80</t>
   </si>
 </sst>
 </file>
@@ -138,7 +138,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -754,8 +754,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1127,7 +1127,7 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="G2">
@@ -1138,6 +1138,9 @@
       </c>
       <c r="I2">
         <v>0</v>
+      </c>
+      <c r="L2">
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:12">
@@ -1153,7 +1156,7 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G3">
@@ -1164,6 +1167,9 @@
       </c>
       <c r="I3">
         <v>4</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:12">
@@ -1179,7 +1185,7 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G4">
@@ -1190,6 +1196,9 @@
       </c>
       <c r="I4">
         <v>0</v>
+      </c>
+      <c r="L4">
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:12">
@@ -1217,6 +1226,9 @@
       <c r="I5">
         <v>0</v>
       </c>
+      <c r="L5">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
@@ -1243,6 +1255,9 @@
       <c r="I6">
         <v>0</v>
       </c>
+      <c r="L6">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:12">
       <c r="A7">
@@ -1257,7 +1272,7 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G7">
@@ -1268,6 +1283,9 @@
       </c>
       <c r="I7">
         <v>0</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:12">
@@ -1283,7 +1301,7 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G8">
@@ -1295,8 +1313,11 @@
       <c r="I8">
         <v>0</v>
       </c>
+      <c r="L8">
+        <v>40</v>
+      </c>
     </row>
-    <row r="9" ht="37" customHeight="1" spans="1:12">
+    <row r="9" ht="51" customHeight="1" spans="1:12">
       <c r="A9">
         <v>22002</v>
       </c>
@@ -1309,7 +1330,7 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G9">
@@ -1320,6 +1341,9 @@
       </c>
       <c r="I9">
         <v>0</v>
+      </c>
+      <c r="L9">
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1" spans="1:12">
@@ -1338,7 +1362,7 @@
       <c r="E10">
         <v>100</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G10">
@@ -1349,6 +1373,9 @@
       </c>
       <c r="I10">
         <v>0</v>
+      </c>
+      <c r="L10">
+        <v>40</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:12">
@@ -1364,7 +1391,7 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G11">
@@ -1375,6 +1402,9 @@
       </c>
       <c r="I11">
         <v>5</v>
+      </c>
+      <c r="L11">
+        <v>40</v>
       </c>
     </row>
     <row r="12" ht="29" customHeight="1" spans="1:12">
@@ -1393,7 +1423,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G12">
@@ -1404,6 +1434,9 @@
       </c>
       <c r="I12">
         <v>0</v>
+      </c>
+      <c r="L12">
+        <v>40</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:12">
@@ -1419,7 +1452,7 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G13">
@@ -1430,6 +1463,9 @@
       </c>
       <c r="I13">
         <v>4</v>
+      </c>
+      <c r="L13">
+        <v>40</v>
       </c>
     </row>
     <row r="14" ht="28" spans="1:12">
@@ -1445,7 +1481,7 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="5" t="s">
         <v>26</v>
       </c>
       <c r="G14">
@@ -1456,6 +1492,9 @@
       </c>
       <c r="I14">
         <v>0</v>
+      </c>
+      <c r="L14">
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:12">
@@ -1471,7 +1510,7 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="5" t="s">
         <v>27</v>
       </c>
       <c r="G15">
@@ -1482,6 +1521,9 @@
       </c>
       <c r="I15">
         <v>0</v>
+      </c>
+      <c r="L15">
+        <v>40</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:12">
@@ -1497,7 +1539,7 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G16">
@@ -1508,6 +1550,9 @@
       </c>
       <c r="I16">
         <v>0</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1"/>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -67,55 +67,94 @@
     <t>sale</t>
   </si>
   <si>
-    <t>生枝1，下回合获得你生枝的牌</t>
-  </si>
-  <si>
-    <t>生长4</t>
-  </si>
-  <si>
-    <t>剪枝1，下回合随机获得一个罕见礼物</t>
-  </si>
-  <si>
-    <t>剪枝1，仙台同学的防御属性提升30点</t>
-  </si>
-  <si>
-    <t>剪枝2，攻击属性提升50点</t>
+    <t>nextTurn</t>
+  </si>
+  <si>
+    <t>生枝{make}，也就是下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>生长{add}</t>
+  </si>
+  <si>
+    <t>剪枝{break}，下回合随机获得一个罕见礼物</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,1,2)</t>
+  </si>
+  <si>
+    <t>剪枝{break}，仙台同学的属性三提升30点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(30,2)</t>
+  </si>
+  <si>
+    <t>剪枝{break}，角色的的属性一提升{nature1}点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(50,1)</t>
   </si>
   <si>
     <t>生长，将卡中数值不足12的部分加成到12</t>
   </si>
   <si>
-    <t>生枝3，下回合获得你生枝的牌</t>
-  </si>
-  <si>
-    <t>生枝1，下回合随机获得一个普通礼物</t>
+    <t>beAddedTo(12)</t>
+  </si>
+  <si>
+    <t>生枝{make}，下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>生枝{make}，下回合随机获得一个普通礼物</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,1,1)</t>
   </si>
   <si>
     <t>大破坏</t>
   </si>
   <si>
-    <t>剪枝5，仙台同学的攻击属性，三提升100点</t>
+    <t>剪枝{break}，仙台同学的属性一，属性三提升{nature1}点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(100,1);addNatureAtSum(100,3)</t>
   </si>
   <si>
     <t>若卡组中有三个以上相同的礼物，生长40，否则生长5</t>
   </si>
   <si>
+    <t>addWithSame(3,40,5)</t>
+  </si>
+  <si>
     <t>凭空</t>
   </si>
   <si>
     <t>若手中没有礼物牌，则随机获得一个罕见礼物卡</t>
   </si>
   <si>
-    <t>生长4，此牌生长的数值提升4</t>
-  </si>
-  <si>
-    <t>剪枝1，若此礼物包含攻击属性的加成，提升防御属性40点</t>
+    <t>addRandomCardIfNot(1,1,2)</t>
+  </si>
+  <si>
+    <t>生长{add}，此牌生长的数值提升4</t>
+  </si>
+  <si>
+    <t>addAddNum(4)</t>
+  </si>
+  <si>
+    <t>剪枝{break}，若此礼物包含属性一的加成，提升属性二40点</t>
+  </si>
+  <si>
+    <t>addNatureAtSumIf(40,1)</t>
   </si>
   <si>
     <t>将手牌中的所有礼物都变成同一个随机礼物</t>
   </si>
   <si>
+    <t>changeHandGift()</t>
+  </si>
+  <si>
     <t>若卡组中有6个以上相同的礼物，生长所有相同的礼物80</t>
+  </si>
+  <si>
+    <t>addWIthSameTogether(6,80)</t>
   </si>
 </sst>
 </file>
@@ -1068,15 +1107,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="1" customWidth="1"/>
     <col min="6" max="6" width="31.5454545454545" style="1" customWidth="1"/>
     <col min="9" max="9" width="11.9090909090909" customWidth="1"/>
+    <col min="10" max="10" width="16.1818181818182" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.8181818181818" customWidth="1"/>
+    <col min="12" max="12" width="11.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1104,7 +1146,7 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
@@ -1113,8 +1155,11 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" ht="28" spans="1:13">
       <c r="A2">
         <v>21001</v>
       </c>
@@ -1128,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1143,7 +1188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:12">
+    <row r="3" ht="20" customHeight="1" spans="1:13">
       <c r="A3">
         <v>21002</v>
       </c>
@@ -1157,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1172,7 +1217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" ht="28" spans="1:12">
+    <row r="4" ht="27" customHeight="1" spans="1:13">
       <c r="A4">
         <v>21003</v>
       </c>
@@ -1186,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1200,8 +1245,11 @@
       <c r="L4">
         <v>20</v>
       </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" ht="28" spans="1:12">
+    <row r="5" ht="28" spans="1:13">
       <c r="A5">
         <v>21004</v>
       </c>
@@ -1215,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1226,11 +1274,14 @@
       <c r="I5">
         <v>0</v>
       </c>
+      <c r="J5" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="L5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" ht="28" spans="1:13">
       <c r="A6">
         <v>21005</v>
       </c>
@@ -1244,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1255,11 +1306,14 @@
       <c r="I6">
         <v>0</v>
       </c>
+      <c r="J6" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="L6">
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:12">
+    <row r="7" ht="30" customHeight="1" spans="1:13">
       <c r="A7">
         <v>21006</v>
       </c>
@@ -1273,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1283,12 +1337,15 @@
       </c>
       <c r="I7">
         <v>0</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="L7">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1" spans="1:12">
+    <row r="8" ht="27" customHeight="1" spans="1:13">
       <c r="A8">
         <v>22001</v>
       </c>
@@ -1302,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1317,7 +1374,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" ht="51" customHeight="1" spans="1:12">
+    <row r="9" ht="51" customHeight="1" spans="1:13">
       <c r="A9">
         <v>22002</v>
       </c>
@@ -1331,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1345,13 +1402,16 @@
       <c r="L9">
         <v>40</v>
       </c>
+      <c r="M9" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="10" ht="27" customHeight="1" spans="1:12">
+    <row r="10" ht="27" customHeight="1" spans="1:13">
       <c r="A10">
         <v>22003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -1363,7 +1423,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1374,11 +1434,14 @@
       <c r="I10">
         <v>0</v>
       </c>
+      <c r="J10" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="L10">
         <v>40</v>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1" spans="1:12">
+    <row r="11" ht="38" customHeight="1" spans="1:13">
       <c r="A11">
         <v>22004</v>
       </c>
@@ -1392,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1401,18 +1464,21 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="L11">
         <v>40</v>
       </c>
     </row>
-    <row r="12" ht="29" customHeight="1" spans="1:12">
+    <row r="12" ht="29" customHeight="1" spans="1:13">
       <c r="A12">
         <v>22005</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1424,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1434,12 +1500,15 @@
       </c>
       <c r="I12">
         <v>0</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="L12">
         <v>40</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:12">
+    <row r="13" ht="24" customHeight="1" spans="1:13">
       <c r="A13">
         <v>22006</v>
       </c>
@@ -1453,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1464,11 +1533,14 @@
       <c r="I13">
         <v>4</v>
       </c>
+      <c r="J13" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="L13">
         <v>40</v>
       </c>
     </row>
-    <row r="14" ht="28" spans="1:12">
+    <row r="14" ht="28" spans="1:13">
       <c r="A14">
         <v>22007</v>
       </c>
@@ -1482,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1493,11 +1565,14 @@
       <c r="I14">
         <v>0</v>
       </c>
+      <c r="J14" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="L14">
         <v>40</v>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1" spans="1:12">
+    <row r="15" ht="33" customHeight="1" spans="1:13">
       <c r="A15">
         <v>22008</v>
       </c>
@@ -1511,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1521,12 +1596,15 @@
       </c>
       <c r="I15">
         <v>0</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="L15">
         <v>40</v>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" spans="1:12">
+    <row r="16" ht="36" customHeight="1" spans="1:13">
       <c r="A16">
         <v>23001</v>
       </c>
@@ -1540,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1550,6 +1628,9 @@
       </c>
       <c r="I16">
         <v>0</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L16">
         <v>100</v>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -49,13 +49,13 @@
     <t>description</t>
   </si>
   <si>
-    <t>make</t>
-  </si>
-  <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>add</t>
+    <t>made</t>
+  </si>
+  <si>
+    <t>broken</t>
+  </si>
+  <si>
+    <t>added</t>
   </si>
   <si>
     <t>trigger</t>
@@ -155,6 +155,15 @@
   </si>
   <si>
     <t>addWIthSameTogether(6,80)</t>
+  </si>
+  <si>
+    <t>测试用例</t>
+  </si>
+  <si>
+    <t>beAdded(4,1)</t>
+  </si>
+  <si>
+    <t>beAddedTo(4,1)</t>
   </si>
 </sst>
 </file>
@@ -167,14 +176,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,12 +329,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -647,138 +655,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -793,7 +804,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1107,34 +1124,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="12.4545454545455" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.5454545454545" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
+    <col min="6" max="6" width="31.5454545454545" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.9090909090909" customWidth="1"/>
-    <col min="10" max="10" width="16.1818181818182" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1818181818182" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.8181818181818" customWidth="1"/>
     <col min="12" max="12" width="11.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -1146,13 +1163,13 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -1172,7 +1189,7 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G2">
@@ -1201,7 +1218,7 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G3">
@@ -1230,7 +1247,7 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="G4">
@@ -1262,7 +1279,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G5">
@@ -1274,7 +1291,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="L5">
@@ -1294,7 +1311,7 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G6">
@@ -1306,7 +1323,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="L6">
@@ -1326,7 +1343,7 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>21</v>
       </c>
       <c r="G7">
@@ -1338,7 +1355,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L7">
@@ -1358,7 +1375,7 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="G8">
@@ -1387,7 +1404,7 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G9">
@@ -1410,7 +1427,7 @@
       <c r="A10">
         <v>22003</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C10">
@@ -1422,7 +1439,7 @@
       <c r="E10">
         <v>100</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G10">
@@ -1434,7 +1451,7 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="L10">
@@ -1454,7 +1471,7 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G11">
@@ -1466,7 +1483,7 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="L11">
@@ -1477,7 +1494,7 @@
       <c r="A12">
         <v>22005</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C12">
@@ -1489,7 +1506,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G12">
@@ -1501,7 +1518,7 @@
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="L12">
@@ -1521,7 +1538,7 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>34</v>
       </c>
       <c r="G13">
@@ -1533,7 +1550,7 @@
       <c r="I13">
         <v>4</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="L13">
@@ -1553,7 +1570,7 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G14">
@@ -1565,7 +1582,7 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="L14">
@@ -1585,7 +1602,7 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G15">
@@ -1597,46 +1614,208 @@
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="2" t="s">
         <v>39</v>
       </c>
       <c r="L15">
         <v>40</v>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" spans="1:13">
-      <c r="A16">
+    <row r="16" s="1" customFormat="1" ht="36" customHeight="1" spans="1:13">
+      <c r="A16" s="1">
         <v>23001</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1" t="s">
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1" spans="1:10">
+      <c r="A17">
+        <v>22201</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18">
+        <v>22202</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:10">
+      <c r="A19">
+        <v>22203</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20">
+        <v>22204</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21">
+        <v>22205</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22">
+        <v>22206</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23">
+        <v>22207</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24">
+        <v>22208</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25">
+        <v>22209</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,13 +49,13 @@
     <t>description</t>
   </si>
   <si>
-    <t>make</t>
-  </si>
-  <si>
-    <t>break</t>
-  </si>
-  <si>
-    <t>add</t>
+    <t>made</t>
+  </si>
+  <si>
+    <t>broken</t>
+  </si>
+  <si>
+    <t>added</t>
   </si>
   <si>
     <t>trigger</t>
@@ -167,14 +167,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -647,133 +640,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -793,7 +786,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -155,15 +155,6 @@
   </si>
   <si>
     <t>addWIthSameTogether(6,80)</t>
-  </si>
-  <si>
-    <t>测试用例</t>
-  </si>
-  <si>
-    <t>beAdded(4,1)</t>
-  </si>
-  <si>
-    <t>beAddedTo(4,1)</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1115,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
@@ -1652,168 +1643,6 @@
       </c>
       <c r="L16" s="1">
         <v>100</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:10">
-      <c r="A17">
-        <v>22201</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18">
-        <v>22202</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" ht="28" spans="1:10">
-      <c r="A19">
-        <v>22203</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20">
-        <v>22204</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21">
-        <v>22205</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22">
-        <v>22206</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23">
-        <v>22207</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24">
-        <v>22208</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25">
-        <v>22209</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>id</t>
   </si>
@@ -70,46 +70,73 @@
     <t>nextTurn</t>
   </si>
   <si>
-    <t>生枝{make}，也就是下回合获得你生枝的牌</t>
-  </si>
-  <si>
-    <t>生长{add}</t>
-  </si>
-  <si>
-    <t>剪枝{break}，下回合随机获得一个罕见礼物</t>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>萌发新芽</t>
+  </si>
+  <si>
+    <t>生枝{made}，也就是下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>木纹渐深</t>
+  </si>
+  <si>
+    <t>生长{added}</t>
+  </si>
+  <si>
+    <t>去芜存菁</t>
+  </si>
+  <si>
+    <t>剪枝{broken}，下回合随机获得一个罕见礼物</t>
   </si>
   <si>
     <t>addRandomCard(1,1,2)</t>
   </si>
   <si>
-    <t>剪枝{break}，仙台同学的属性三提升30点</t>
+    <t>霜打残叶</t>
+  </si>
+  <si>
+    <t>剪枝{broken}，仙台同学的属性三提升30点</t>
   </si>
   <si>
     <t>addNatureAtSum(30,2)</t>
   </si>
   <si>
-    <t>剪枝{break}，角色的的属性一提升{nature1}点</t>
+    <t>刈除侧蔓</t>
+  </si>
+  <si>
+    <t>剪枝{broken}，角色的的属性一提升{nature1}点</t>
   </si>
   <si>
     <t>addNatureAtSum(50,1)</t>
   </si>
   <si>
+    <t>拔节有声</t>
+  </si>
+  <si>
     <t>生长，将卡中数值不足12的部分加成到12</t>
   </si>
   <si>
     <t>beAddedTo(12)</t>
   </si>
   <si>
-    <t>生枝{make}，下回合获得你生枝的牌</t>
-  </si>
-  <si>
-    <t>生枝{make}，下回合随机获得一个普通礼物</t>
+    <t>抽枝散叶</t>
+  </si>
+  <si>
+    <t>生枝{made}，下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>节外生枝</t>
+  </si>
+  <si>
+    <t>生枝{made}，下回合随机获得一个普通礼物</t>
   </si>
   <si>
     <t>addRandomCard(1,1,1)</t>
   </si>
   <si>
-    <t>大破坏</t>
+    <t>剪除枯枝</t>
   </si>
   <si>
     <t>剪枝{break}，仙台同学的属性一，属性三提升{nature1}点</t>
@@ -118,13 +145,16 @@
     <t>addNatureAtSum(100,1);addNatureAtSum(100,3)</t>
   </si>
   <si>
+    <t>蒸腾不息</t>
+  </si>
+  <si>
     <t>若卡组中有三个以上相同的礼物，生长40，否则生长5</t>
   </si>
   <si>
     <t>addWithSame(3,40,5)</t>
   </si>
   <si>
-    <t>凭空</t>
+    <t>枝头吐绿</t>
   </si>
   <si>
     <t>若手中没有礼物牌，则随机获得一个罕见礼物卡</t>
@@ -133,22 +163,34 @@
     <t>addRandomCardIfNot(1,1,2)</t>
   </si>
   <si>
-    <t>生长{add}，此牌生长的数值提升4</t>
+    <t>顶梢争高</t>
+  </si>
+  <si>
+    <t>生长{added}，此牌生长的数值提升4</t>
   </si>
   <si>
     <t>addAddNum(4)</t>
   </si>
   <si>
-    <t>剪枝{break}，若此礼物包含属性一的加成，提升属性二40点</t>
+    <t>修枝整形</t>
+  </si>
+  <si>
+    <t>剪枝{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
   </si>
   <si>
     <t>addNatureAtSumIf(40,1)</t>
   </si>
   <si>
+    <t>丛生之态</t>
+  </si>
+  <si>
     <t>将手牌中的所有礼物都变成同一个随机礼物</t>
   </si>
   <si>
     <t>changeHandGift()</t>
+  </si>
+  <si>
+    <t>晨露润泽</t>
   </si>
   <si>
     <t>若卡组中有6个以上相同的礼物，生长所有相同的礼物80</t>
@@ -167,13 +209,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -646,137 +694,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -795,14 +843,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1115,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
@@ -1126,7 +1177,7 @@
     <col min="12" max="12" width="11.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1166,11 +1217,17 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" ht="28" spans="1:13">
+    <row r="2" ht="28" spans="1:14">
       <c r="A2">
         <v>21001</v>
       </c>
+      <c r="B2" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="C2">
         <v>0</v>
       </c>
@@ -1180,8 +1237,8 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>13</v>
+      <c r="F2" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1196,10 +1253,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:13">
+    <row r="3" ht="20" customHeight="1" spans="1:14">
       <c r="A3">
         <v>21002</v>
       </c>
+      <c r="B3" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="C3">
         <v>0</v>
       </c>
@@ -1209,8 +1269,8 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>14</v>
+      <c r="F3" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1225,10 +1285,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" ht="27" customHeight="1" spans="1:13">
+    <row r="4" ht="27" customHeight="1" spans="1:14">
       <c r="A4">
         <v>21003</v>
       </c>
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="C4">
         <v>0</v>
       </c>
@@ -1238,8 +1301,8 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>15</v>
+      <c r="F4" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1254,13 +1317,16 @@
         <v>20</v>
       </c>
       <c r="M4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:13">
+    <row r="5" ht="28" spans="1:14">
       <c r="A5">
         <v>21004</v>
       </c>
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="C5">
         <v>0</v>
       </c>
@@ -1270,8 +1336,8 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>17</v>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1283,16 +1349,19 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="28" spans="1:13">
+    <row r="6" ht="28" spans="1:14">
       <c r="A6">
         <v>21005</v>
       </c>
+      <c r="B6" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="C6">
         <v>50</v>
       </c>
@@ -1302,8 +1371,8 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>19</v>
+      <c r="F6" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1315,16 +1384,19 @@
         <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L6">
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:13">
+    <row r="7" ht="30" customHeight="1" spans="1:14">
       <c r="A7">
         <v>21006</v>
       </c>
+      <c r="B7" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="C7">
         <v>0</v>
       </c>
@@ -1334,8 +1406,8 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>21</v>
+      <c r="F7" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1347,16 +1419,19 @@
         <v>0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="27" customHeight="1" spans="1:13">
+    <row r="8" ht="27" customHeight="1" spans="1:14">
       <c r="A8">
         <v>22001</v>
       </c>
+      <c r="B8" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="C8">
         <v>0</v>
       </c>
@@ -1366,8 +1441,8 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>23</v>
+      <c r="F8" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1382,10 +1457,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" ht="51" customHeight="1" spans="1:13">
+    <row r="9" ht="51" customHeight="1" spans="1:14">
       <c r="A9">
         <v>22002</v>
       </c>
+      <c r="B9" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="C9">
         <v>0</v>
       </c>
@@ -1395,8 +1473,8 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>24</v>
+      <c r="F9" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1411,15 +1489,15 @@
         <v>40</v>
       </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="10" ht="27" customHeight="1" spans="1:13">
+    <row r="10" ht="27" customHeight="1" spans="1:14">
       <c r="A10">
         <v>22003</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
+      <c r="B10" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -1430,8 +1508,8 @@
       <c r="E10">
         <v>100</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>27</v>
+      <c r="F10" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1443,16 +1521,19 @@
         <v>0</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L10">
         <v>40</v>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1" spans="1:13">
+    <row r="11" ht="38" customHeight="1" spans="1:14">
       <c r="A11">
         <v>22004</v>
       </c>
+      <c r="B11" s="6" t="s">
+        <v>38</v>
+      </c>
       <c r="C11">
         <v>0</v>
       </c>
@@ -1462,8 +1543,8 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>29</v>
+      <c r="F11" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1475,18 +1556,18 @@
         <v>0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L11">
         <v>40</v>
       </c>
     </row>
-    <row r="12" ht="29" customHeight="1" spans="1:13">
+    <row r="12" ht="29" customHeight="1" spans="1:14">
       <c r="A12">
         <v>22005</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>31</v>
+      <c r="B12" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1497,8 +1578,8 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>32</v>
+      <c r="F12" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1510,16 +1591,19 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L12">
         <v>40</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:13">
+    <row r="13" ht="24" customHeight="1" spans="1:14">
       <c r="A13">
         <v>22006</v>
       </c>
+      <c r="B13" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="C13">
         <v>0</v>
       </c>
@@ -1529,8 +1613,8 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>34</v>
+      <c r="F13" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1542,16 +1626,19 @@
         <v>4</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L13">
         <v>40</v>
       </c>
     </row>
-    <row r="14" ht="28" spans="1:13">
+    <row r="14" ht="28" spans="1:14">
       <c r="A14">
         <v>22007</v>
       </c>
+      <c r="B14" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="C14">
         <v>0</v>
       </c>
@@ -1561,8 +1648,8 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>36</v>
+      <c r="F14" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1574,16 +1661,19 @@
         <v>0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="L14">
         <v>40</v>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1" spans="1:13">
+    <row r="15" ht="33" customHeight="1" spans="1:14">
       <c r="A15">
         <v>22008</v>
       </c>
+      <c r="B15" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="C15">
         <v>0</v>
       </c>
@@ -1593,8 +1683,8 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>38</v>
+      <c r="F15" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1606,17 +1696,19 @@
         <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="L15">
         <v>40</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="36" customHeight="1" spans="1:13">
+    <row r="16" s="1" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A16" s="1">
         <v>23001</v>
       </c>
-      <c r="B16" s="7"/>
+      <c r="B16" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="C16" s="1">
         <v>0</v>
       </c>
@@ -1627,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1638,8 +1730,8 @@
       <c r="I16" s="1">
         <v>0</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>41</v>
+      <c r="J16" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="L16" s="1">
         <v>100</v>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
   <si>
     <t>id</t>
   </si>
@@ -70,54 +70,87 @@
     <t>nextTurn</t>
   </si>
   <si>
-    <t>生枝{make}，也就是下回合获得你生枝的牌</t>
-  </si>
-  <si>
-    <t>生长{add}</t>
-  </si>
-  <si>
-    <t>剪枝{break}，下回合随机获得一个罕见礼物</t>
+    <t>初始功能牌</t>
+  </si>
+  <si>
+    <t>生枝{made}</t>
+  </si>
+  <si>
+    <t>萌发新芽</t>
+  </si>
+  <si>
+    <t>生枝{made}，也就是下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>丛生之态</t>
+  </si>
+  <si>
+    <t>生长{added}</t>
+  </si>
+  <si>
+    <t>去芜存菁</t>
+  </si>
+  <si>
+    <t>剪枝{broken}，下回合随机获得一个罕见礼物</t>
   </si>
   <si>
     <t>addRandomCard(1,1,2)</t>
   </si>
   <si>
-    <t>剪枝{break}，仙台同学的属性三提升30点</t>
+    <t>刈除侧蔓</t>
+  </si>
+  <si>
+    <t>剪枝{broken}，仙台同学的属性三提升30点</t>
   </si>
   <si>
     <t>addNatureAtSum(30,2)</t>
   </si>
   <si>
-    <t>剪枝{break}，角色的的属性一提升{nature1}点</t>
+    <t>修枝整形</t>
+  </si>
+  <si>
+    <t>剪枝{broken}，角色的的属性一提升{nature1}点</t>
   </si>
   <si>
     <t>addNatureAtSum(50,1)</t>
   </si>
   <si>
+    <t>光合积累</t>
+  </si>
+  <si>
     <t>生长，将卡中数值不足12的部分加成到12</t>
   </si>
   <si>
     <t>beAddedTo(12)</t>
   </si>
   <si>
-    <t>生枝{make}，下回合获得你生枝的牌</t>
-  </si>
-  <si>
-    <t>生枝{make}，下回合随机获得一个普通礼物</t>
+    <t>枝条分叉</t>
+  </si>
+  <si>
+    <t>生枝{made}，下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>幼枝初展</t>
+  </si>
+  <si>
+    <t>生枝{made}，下回合随机获得一个普通礼物</t>
   </si>
   <si>
     <t>addRandomCard(1,1,1)</t>
   </si>
   <si>
-    <t>大破坏</t>
-  </si>
-  <si>
-    <t>剪枝{break}，仙台同学的属性一，属性三提升{nature1}点</t>
+    <t>截干蓄势</t>
+  </si>
+  <si>
+    <t>剪枝{broken}，仙台同学的属性一，属性三提升{nature1}点</t>
   </si>
   <si>
     <t>addNatureAtSum(100,1);addNatureAtSum(100,3)</t>
   </si>
   <si>
+    <t>拔节有声</t>
+  </si>
+  <si>
     <t>若卡组中有三个以上相同的礼物，生长40，否则生长5</t>
   </si>
   <si>
@@ -133,22 +166,34 @@
     <t>addRandomCardIfNot(1,1,2)</t>
   </si>
   <si>
-    <t>生长{add}，此牌生长的数值提升4</t>
+    <t>春来发枝</t>
+  </si>
+  <si>
+    <t>生长{added}，此牌生长的数值提升4</t>
   </si>
   <si>
     <t>addAddNum(4)</t>
   </si>
   <si>
-    <t>剪枝{break}，若此礼物包含属性一的加成，提升属性二40点</t>
+    <t>整冠截顶</t>
+  </si>
+  <si>
+    <t>剪枝{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
   </si>
   <si>
     <t>addNatureAtSumIf(40,1)</t>
   </si>
   <si>
+    <t>一叶知秋</t>
+  </si>
+  <si>
     <t>将手牌中的所有礼物都变成同一个随机礼物</t>
   </si>
   <si>
     <t>changeHandGift()</t>
+  </si>
+  <si>
+    <t>移花接木</t>
   </si>
   <si>
     <t>若卡组中有6个以上相同的礼物，生长所有相同的礼物80</t>
@@ -176,13 +221,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -655,137 +706,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -804,14 +855,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1124,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
@@ -1176,21 +1233,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="28" spans="1:13">
-      <c r="A2">
-        <v>21001</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>21601</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>13</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1201,13 +1261,16 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:13">
+      <c r="J2" s="4"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" ht="28" spans="1:13">
       <c r="A3">
-        <v>21002</v>
+        <v>21001</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1218,25 +1281,28 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>14</v>
+      <c r="F3" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" ht="27" customHeight="1" spans="1:13">
+    <row r="4" ht="20" customHeight="1" spans="1:13">
       <c r="A4">
-        <v>21003</v>
+        <v>21002</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1247,28 +1313,28 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>15</v>
+      <c r="F4" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>20</v>
       </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" ht="28" spans="1:13">
+    </row>
+    <row r="5" ht="27" customHeight="1" spans="1:13">
       <c r="A5">
-        <v>21004</v>
+        <v>21003</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1279,8 +1345,8 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>17</v>
+      <c r="F5" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1291,19 +1357,22 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="L5">
         <v>20</v>
       </c>
+      <c r="M5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" ht="28" spans="1:13">
       <c r="A6">
-        <v>21005</v>
+        <v>21004</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1311,31 +1380,34 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>19</v>
+      <c r="F6" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L6">
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:13">
+    <row r="7" ht="28" spans="1:13">
       <c r="A7">
-        <v>21006</v>
+        <v>21005</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1343,72 +1415,81 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>21</v>
+      <c r="F7" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L7">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="27" customHeight="1" spans="1:13">
+    <row r="8" ht="30" customHeight="1" spans="1:13">
       <c r="A8">
+        <v>21006</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1" spans="1:13">
+      <c r="A9">
         <v>22001</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8">
+      <c r="B9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9">
         <v>3</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" ht="51" customHeight="1" spans="1:13">
-      <c r="A9">
-        <v>22002</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1419,83 +1500,83 @@
       <c r="L9">
         <v>40</v>
       </c>
-      <c r="M9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" ht="27" customHeight="1" spans="1:13">
+    </row>
+    <row r="10" ht="51" customHeight="1" spans="1:13">
       <c r="A10">
-        <v>22003</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>22002</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>100</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="L10">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" ht="38" customHeight="1" spans="1:13">
+      <c r="M10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1" spans="1:13">
       <c r="A11">
-        <v>22004</v>
+        <v>22003</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>29</v>
+        <v>100</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L11">
         <v>40</v>
       </c>
     </row>
-    <row r="12" ht="29" customHeight="1" spans="1:13">
+    <row r="12" ht="38" customHeight="1" spans="1:13">
       <c r="A12">
-        <v>22005</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>22004</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1506,8 +1587,8 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>32</v>
+      <c r="F12" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1519,15 +1600,18 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L12">
         <v>40</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:13">
+    <row r="13" ht="29" customHeight="1" spans="1:13">
       <c r="A13">
-        <v>22006</v>
+        <v>22005</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1538,8 +1622,8 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>34</v>
+      <c r="F13" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1548,18 +1632,21 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L13">
         <v>40</v>
       </c>
     </row>
-    <row r="14" ht="28" spans="1:13">
+    <row r="14" ht="24" customHeight="1" spans="1:13">
       <c r="A14">
-        <v>22007</v>
+        <v>22006</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1570,28 +1657,31 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>36</v>
+      <c r="F14" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L14">
         <v>40</v>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1" spans="1:13">
+    <row r="15" ht="28" spans="1:13">
       <c r="A15">
-        <v>22008</v>
+        <v>22007</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1602,218 +1692,255 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>38</v>
+      <c r="F15" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L15">
         <v>40</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="36" customHeight="1" spans="1:13">
-      <c r="A16" s="1">
+    <row r="16" ht="33" customHeight="1" spans="1:13">
+      <c r="A16">
+        <v>22008</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:12">
+      <c r="A17" s="1">
         <v>23001</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="1">
-        <v>0</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L16" s="1">
+      <c r="B17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1" spans="1:10">
-      <c r="A17">
+    <row r="18" ht="22" customHeight="1" spans="1:12">
+      <c r="A18">
         <v>22201</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18">
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19">
         <v>22202</v>
       </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:12">
+      <c r="A20">
+        <v>22203</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" ht="28" spans="1:10">
-      <c r="A19">
-        <v>22203</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20">
+    <row r="21" spans="1:12">
+      <c r="A21">
         <v>22204</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21">
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22">
         <v>22205</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23">
         <v>22206</v>
       </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24">
         <v>22207</v>
       </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25">
         <v>22208</v>
       </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25">
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26">
         <v>22209</v>
       </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>42</v>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
   <si>
     <t>id</t>
   </si>
@@ -145,9 +145,6 @@
     <t>剪枝{broken}，仙台同学的属性一，属性三提升{nature1}点</t>
   </si>
   <si>
-    <t>addNatureAtSum(100,1);addNatureAtSum(100,3)</t>
-  </si>
-  <si>
     <t>拔节有声</t>
   </si>
   <si>
@@ -202,13 +199,25 @@
     <t>addWIthSameTogether(6,80)</t>
   </si>
   <si>
-    <t>测试用例</t>
-  </si>
-  <si>
     <t>beAdded(4,1)</t>
   </si>
   <si>
     <t>beAddedTo(4,1)</t>
+  </si>
+  <si>
+    <t>beAddedTo(88,1)</t>
+  </si>
+  <si>
+    <t>测试01@</t>
+  </si>
+  <si>
+    <t>drawCard(2)</t>
+  </si>
+  <si>
+    <t>测试02</t>
+  </si>
+  <si>
+    <t>addNatureAtSumIf(1,2)</t>
   </si>
 </sst>
 </file>
@@ -221,7 +230,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +245,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -380,7 +396,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,6 +406,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2972F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -706,55 +728,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
@@ -769,74 +788,77 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -869,6 +891,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1181,7 +1206,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
@@ -1564,9 +1589,7 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="J11" s="2"/>
       <c r="L11">
         <v>40</v>
       </c>
@@ -1576,31 +1599,31 @@
         <v>22004</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="s">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="L12">
         <v>40</v>
@@ -1611,31 +1634,31 @@
         <v>22005</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="L13">
         <v>40</v>
@@ -1646,19 +1669,19 @@
         <v>22006</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1670,7 +1693,7 @@
         <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L14">
         <v>40</v>
@@ -1681,19 +1704,19 @@
         <v>22007</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1705,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L15">
         <v>40</v>
@@ -1716,31 +1739,31 @@
         <v>22008</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="L16">
         <v>40</v>
@@ -1751,31 +1774,31 @@
         <v>23001</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="1">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="L17" s="1">
         <v>100</v>
@@ -1795,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1818,13 +1841,16 @@
         <v>57</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" ht="28" spans="1:12">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>22203</v>
       </c>
+      <c r="B20" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="C20">
         <v>0</v>
       </c>
@@ -1835,16 +1861,19 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21">
         <v>22204</v>
       </c>
+      <c r="B21" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="C21">
         <v>0</v>
       </c>
@@ -1854,93 +1883,11 @@
       <c r="E21">
         <v>0</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22">
-        <v>22205</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23">
-        <v>22206</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24">
-        <v>22207</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25">
-        <v>22208</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26">
-        <v>22209</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>57</v>
+      <c r="F21" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
   <si>
     <t>id</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>nextTurn</t>
+  </si>
+  <si>
+    <t>dialog</t>
   </si>
   <si>
     <t>初始功能牌</t>
@@ -1206,7 +1209,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
@@ -1215,9 +1218,10 @@
     <col min="10" max="10" width="16.1818181818182" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.8181818181818" customWidth="1"/>
     <col min="12" max="12" width="11.7272727272727" customWidth="1"/>
+    <col min="13" max="13" width="19.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1257,13 +1261,16 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>21601</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -1275,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1289,13 +1296,16 @@
       <c r="J2" s="4"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-    </row>
-    <row r="3" ht="28" spans="1:13">
+      <c r="N2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:14">
       <c r="A3">
         <v>21001</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1307,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1321,13 +1331,16 @@
       <c r="L3">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:13">
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:14">
       <c r="A4">
         <v>21002</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1339,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1353,13 +1366,16 @@
       <c r="L4">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" ht="27" customHeight="1" spans="1:13">
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1" spans="1:14">
       <c r="A5">
         <v>21003</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1371,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1386,15 +1402,18 @@
         <v>20</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" ht="28" spans="1:13">
+        <v>22</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:14">
       <c r="A6">
         <v>21004</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1406,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1418,18 +1437,21 @@
         <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" ht="28" spans="1:13">
+      <c r="N6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:14">
       <c r="A7">
         <v>21005</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -1441,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1453,18 +1475,21 @@
         <v>0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:13">
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:14">
       <c r="A8">
         <v>21006</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1476,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1488,18 +1513,21 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L8">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" ht="27" customHeight="1" spans="1:13">
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1" spans="1:14">
       <c r="A9">
         <v>22001</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1511,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -1525,13 +1553,16 @@
       <c r="L9">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" ht="51" customHeight="1" spans="1:13">
+      <c r="N9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1" spans="1:14">
       <c r="A10">
         <v>22002</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1543,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1558,15 +1589,18 @@
         <v>40</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1" spans="1:13">
+        <v>36</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1" spans="1:14">
       <c r="A11">
         <v>22003</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1578,7 +1612,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1589,17 +1623,19 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="2"/>
       <c r="L11">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" ht="38" customHeight="1" spans="1:13">
+      <c r="N11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1" spans="1:14">
       <c r="A12">
         <v>22004</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1611,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1623,18 +1659,21 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L12">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" ht="29" customHeight="1" spans="1:13">
+      <c r="N12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="29" customHeight="1" spans="1:14">
       <c r="A13">
         <v>22005</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1646,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1658,18 +1697,21 @@
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L13">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:13">
+      <c r="N13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:14">
       <c r="A14">
         <v>22006</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1681,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1693,18 +1735,21 @@
         <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L14">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" ht="28" spans="1:13">
+      <c r="N14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" ht="28" spans="1:14">
       <c r="A15">
         <v>22007</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1716,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1728,18 +1773,21 @@
         <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L15">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" ht="33" customHeight="1" spans="1:13">
+      <c r="N15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="33" customHeight="1" spans="1:14">
       <c r="A16">
         <v>22008</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1751,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1763,18 +1811,21 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L16">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:12">
+      <c r="N16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A17" s="1">
         <v>23001</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -1786,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1798,13 +1849,16 @@
         <v>0</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L17" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:12">
+      <c r="N17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:14">
       <c r="A18">
         <v>22201</v>
       </c>
@@ -1818,13 +1872,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>22202</v>
       </c>
@@ -1838,18 +1892,18 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>22203</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1861,18 +1915,18 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>22204</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1884,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1929,7 +1929,7 @@
         <v>62</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>0</v>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -1297,7 +1297,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="N2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:14">
@@ -1332,7 +1332,7 @@
         <v>20</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:14">
@@ -1367,7 +1367,7 @@
         <v>20</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="27" customHeight="1" spans="1:14">
@@ -1405,7 +1405,7 @@
         <v>22</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:14">
@@ -1443,7 +1443,7 @@
         <v>20</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:14">
@@ -1481,7 +1481,7 @@
         <v>20</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:14">
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1" spans="1:14">
@@ -1554,7 +1554,7 @@
         <v>40</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="51" customHeight="1" spans="1:14">
@@ -1592,7 +1592,7 @@
         <v>36</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1" spans="1:14">
@@ -1627,7 +1627,7 @@
         <v>40</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:14">
@@ -1665,7 +1665,7 @@
         <v>40</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="29" customHeight="1" spans="1:14">
@@ -1703,7 +1703,7 @@
         <v>40</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:14">
@@ -1779,7 +1779,7 @@
         <v>40</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="33" customHeight="1" spans="1:14">
@@ -1817,7 +1817,7 @@
         <v>40</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:14">
@@ -1855,7 +1855,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:14">

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>id</t>
   </si>
@@ -103,7 +103,7 @@
     <t>刈除侧蔓</t>
   </si>
   <si>
-    <t>剪枝{broken}，仙台同学的属性三提升30点</t>
+    <t>剪枝{broken}，蒂娜的属性三提升30点</t>
   </si>
   <si>
     <t>addNatureAtSum(30,2)</t>
@@ -112,7 +112,7 @@
     <t>修枝整形</t>
   </si>
   <si>
-    <t>剪枝{broken}，角色的的属性一提升{nature1}点</t>
+    <t>剪枝{broken}，蒂娜的的属性一提升{nature1}点</t>
   </si>
   <si>
     <t>addNatureAtSum(50,1)</t>
@@ -145,7 +145,7 @@
     <t>截干蓄势</t>
   </si>
   <si>
-    <t>剪枝{broken}，仙台同学的属性一，属性三提升{nature1}点</t>
+    <t>剪枝{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
   </si>
   <si>
     <t>拔节有声</t>
@@ -200,27 +200,6 @@
   </si>
   <si>
     <t>addWIthSameTogether(6,80)</t>
-  </si>
-  <si>
-    <t>beAdded(4,1)</t>
-  </si>
-  <si>
-    <t>beAddedTo(4,1)</t>
-  </si>
-  <si>
-    <t>beAddedTo(88,1)</t>
-  </si>
-  <si>
-    <t>测试01@</t>
-  </si>
-  <si>
-    <t>drawCard(2)</t>
-  </si>
-  <si>
-    <t>测试02</t>
-  </si>
-  <si>
-    <t>addNatureAtSumIf(1,2)</t>
   </si>
 </sst>
 </file>
@@ -233,7 +212,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,13 +227,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -399,7 +371,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -409,12 +381,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2972F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,52 +697,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
@@ -791,77 +760,74 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -894,9 +860,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1209,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
@@ -1856,92 +1819,6 @@
       </c>
       <c r="N17">
         <v>15</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:14">
-      <c r="A18">
-        <v>22201</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19">
-        <v>22202</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20">
-        <v>22203</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21">
-        <v>22204</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -94,7 +94,7 @@
     <t>去芜存菁</t>
   </si>
   <si>
-    <t>剪枝{broken}，下回合随机获得一个罕见礼物</t>
+    <t>剪枝{broken}，本回合随机获得一张罕见礼物卡</t>
   </si>
   <si>
     <t>addRandomCard(1,1,2)</t>
@@ -136,7 +136,7 @@
     <t>幼枝初展</t>
   </si>
   <si>
-    <t>生枝{made}，下回合随机获得一个普通礼物</t>
+    <t>生枝{made}，本回合随机获得一张普通属性卡</t>
   </si>
   <si>
     <t>addRandomCard(1,1,1)</t>
@@ -1361,12 +1361,13 @@
       <c r="I5">
         <v>0</v>
       </c>
+      <c r="J5" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="L5">
         <v>20</v>
       </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
+      <c r="M5"/>
       <c r="N5">
         <v>9</v>
       </c>
@@ -1548,12 +1549,13 @@
       <c r="I10">
         <v>0</v>
       </c>
+      <c r="J10" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="L10">
         <v>40</v>
       </c>
-      <c r="M10" t="s">
-        <v>36</v>
-      </c>
+      <c r="M10"/>
       <c r="N10">
         <v>6</v>
       </c>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -1367,7 +1367,6 @@
       <c r="L5">
         <v>20</v>
       </c>
-      <c r="M5"/>
       <c r="N5">
         <v>9</v>
       </c>
@@ -1555,7 +1554,6 @@
       <c r="L10">
         <v>40</v>
       </c>
-      <c r="M10"/>
       <c r="N10">
         <v>6</v>
       </c>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
   <si>
     <t>id</t>
   </si>
@@ -49,6 +49,9 @@
     <t>description</t>
   </si>
   <si>
+    <t>text</t>
+  </si>
+  <si>
     <t>made</t>
   </si>
   <si>
@@ -76,34 +79,43 @@
     <t>初始功能牌</t>
   </si>
   <si>
-    <t>生枝{made}</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生枝{made}</t>
+  </si>
+  <si>
+    <t>卡牌介绍占坑</t>
+  </si>
+  <si>
+    <t>beMade(2)</t>
   </si>
   <si>
     <t>萌发新芽</t>
   </si>
   <si>
-    <t>生枝{made}，也就是下回合获得你生枝的牌</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生枝{made}，也就是下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>shake(1,0.2)</t>
   </si>
   <si>
     <t>丛生之态</t>
   </si>
   <si>
-    <t>生长{added}</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生长{added}</t>
   </si>
   <si>
     <t>去芜存菁</t>
   </si>
   <si>
-    <t>剪枝{broken}，本回合随机获得一张罕见礼物卡</t>
-  </si>
-  <si>
-    <t>addRandomCard(1,1,2)</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，本回合随机获得一张罕见礼物卡</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,1,2);magnify(0.2)</t>
   </si>
   <si>
     <t>刈除侧蔓</t>
   </si>
   <si>
-    <t>剪枝{broken}，蒂娜的属性三提升30点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的属性三提升30点</t>
   </si>
   <si>
     <t>addNatureAtSum(30,2)</t>
@@ -112,7 +124,7 @@
     <t>修枝整形</t>
   </si>
   <si>
-    <t>剪枝{broken}，蒂娜的的属性一提升{nature1}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的的属性一提升{nature1}点</t>
   </si>
   <si>
     <t>addNatureAtSum(50,1)</t>
@@ -121,46 +133,46 @@
     <t>光合积累</t>
   </si>
   <si>
-    <t>生长，将卡中数值不足12的部分加成到12</t>
-  </si>
-  <si>
-    <t>beAddedTo(12)</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生长，将卡中数值不足12的部分加成到12</t>
+  </si>
+  <si>
+    <t>beAddedTo(12);shake(1,0.2)</t>
   </si>
   <si>
     <t>枝条分叉</t>
   </si>
   <si>
-    <t>生枝{made}，下回合获得你生枝的牌</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生枝{made}，下回合获得你生枝的牌</t>
   </si>
   <si>
     <t>幼枝初展</t>
   </si>
   <si>
-    <t>生枝{made}，本回合随机获得一张普通属性卡</t>
-  </si>
-  <si>
-    <t>addRandomCard(1,1,1)</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生枝{made}，本回合随机获得一张普通属性卡</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,1,1);shake(1,0.2)</t>
   </si>
   <si>
     <t>截干蓄势</t>
   </si>
   <si>
-    <t>剪枝{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
   </si>
   <si>
     <t>拔节有声</t>
   </si>
   <si>
-    <t>若卡组中有三个以上相同的礼物，生长40，否则生长5</t>
-  </si>
-  <si>
-    <t>addWithSame(3,40,5)</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若卡组中有三个以上相同的礼物，生长40，否则生长5</t>
+  </si>
+  <si>
+    <t>addWithSame(3,40,5);magnify(0.3)</t>
   </si>
   <si>
     <t>凭空</t>
   </si>
   <si>
-    <t>若手中没有礼物牌，则随机获得一个罕见礼物卡</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若手中没有礼物牌，则随机获得一个罕见礼物卡</t>
   </si>
   <si>
     <t>addRandomCardIfNot(1,1,2)</t>
@@ -169,25 +181,25 @@
     <t>春来发枝</t>
   </si>
   <si>
-    <t>生长{added}，此牌生长的数值提升4</t>
-  </si>
-  <si>
-    <t>addAddNum(4)</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生长{added}，此牌生长的数值提升4</t>
+  </si>
+  <si>
+    <t>addAddNum(4);magnify(0.2)</t>
   </si>
   <si>
     <t>整冠截顶</t>
   </si>
   <si>
-    <t>剪枝{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
-  </si>
-  <si>
-    <t>addNatureAtSumIf(40,1)</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
+  </si>
+  <si>
+    <t>addNatureAtSumIf(40,1);shake(1,0.3)</t>
   </si>
   <si>
     <t>一叶知秋</t>
   </si>
   <si>
-    <t>将手牌中的所有礼物都变成同一个随机礼物</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 将手牌中的所有礼物都变成同一个随机礼物</t>
   </si>
   <si>
     <t>changeHandGift()</t>
@@ -196,10 +208,22 @@
     <t>移花接木</t>
   </si>
   <si>
-    <t>若卡组中有6个以上相同的礼物，生长所有相同的礼物80</t>
-  </si>
-  <si>
-    <t>addWIthSameTogether(6,80)</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 若卡组中有6个以上相同的礼物，生长所有相同的礼物80</t>
+  </si>
+  <si>
+    <t>addWIthSameTogether(6,80);magnify(0.5)</t>
+  </si>
+  <si>
+    <t>测试卡牌</t>
+  </si>
+  <si>
+    <t>beMade(3)</t>
+  </si>
+  <si>
+    <t>beMade(4)</t>
+  </si>
+  <si>
+    <t>beMade(5)</t>
   </si>
 </sst>
 </file>
@@ -1172,19 +1196,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
     <col min="6" max="6" width="31.5454545454545" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.9090909090909" customWidth="1"/>
-    <col min="10" max="10" width="16.1818181818182" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.8181818181818" customWidth="1"/>
-    <col min="12" max="12" width="11.7272727272727" customWidth="1"/>
-    <col min="13" max="13" width="19.3636363636364" customWidth="1"/>
+    <col min="7" max="7" width="16.9090909090909" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.9090909090909" customWidth="1"/>
+    <col min="11" max="11" width="16.1818181818182" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.8181818181818" customWidth="1"/>
+    <col min="13" max="13" width="11.7272727272727" customWidth="1"/>
+    <col min="14" max="14" width="19.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1203,7 +1228,7 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1212,28 +1237,31 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" ht="28" spans="1:15">
       <c r="A2" s="3">
         <v>21601</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -1245,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1256,19 +1284,24 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="3"/>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="L2" s="3"/>
-      <c r="N2">
+      <c r="M2" s="3"/>
+      <c r="O2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="28" spans="1:14">
+    <row r="3" ht="42" spans="1:15">
       <c r="A3">
         <v>21001</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1280,30 +1313,36 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="L3">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
         <v>20</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:14">
+    <row r="4" ht="20" customHeight="1" spans="1:15">
       <c r="A4">
         <v>21002</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1315,68 +1354,74 @@
         <v>0</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>4</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>20</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="27" customHeight="1" spans="1:14">
+    <row r="5" ht="27" customHeight="1" spans="1:15">
       <c r="A5">
         <v>21003</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
         <v>20</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5">
-        <v>20</v>
-      </c>
-      <c r="N5">
+      <c r="O5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="28" spans="1:14">
+    <row r="6" ht="42" spans="1:15">
       <c r="A6">
         <v>21004</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1388,33 +1433,36 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6">
         <v>20</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="28" spans="1:14">
+    <row r="7" ht="42" spans="1:15">
       <c r="A7">
         <v>21005</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -1426,33 +1474,36 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>2</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7">
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7">
         <v>20</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" spans="1:14">
+    <row r="8" ht="30" customHeight="1" spans="1:15">
       <c r="A8">
         <v>21006</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1464,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1475,22 +1526,25 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8">
         <v>20</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="27" customHeight="1" spans="1:14">
+    <row r="9" ht="27" customHeight="1" spans="1:15">
       <c r="A9">
         <v>22001</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1502,30 +1556,33 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9">
+        <v>37</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9">
         <v>3</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="L9">
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>40</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" ht="51" customHeight="1" spans="1:14">
+    <row r="10" ht="51" customHeight="1" spans="1:15">
       <c r="A10">
         <v>22002</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1537,33 +1594,36 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10">
+        <v>39</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10">
         <v>1</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10">
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N10">
+      <c r="M10">
+        <v>40</v>
+      </c>
+      <c r="O10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="27" customHeight="1" spans="1:14">
+    <row r="11" ht="27" customHeight="1" spans="1:15">
       <c r="A11">
         <v>22003</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1575,30 +1635,36 @@
         <v>100</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>5</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="L11">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11">
         <v>40</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1" spans="1:14">
+    <row r="12" ht="38" customHeight="1" spans="1:15">
       <c r="A12">
         <v>22004</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1610,33 +1676,36 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12">
         <v>40</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12">
-        <v>40</v>
-      </c>
-      <c r="N12">
+      <c r="O12">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="29" customHeight="1" spans="1:14">
+    <row r="13" ht="29" customHeight="1" spans="1:15">
       <c r="A13">
         <v>22005</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1648,10 +1717,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1659,22 +1728,25 @@
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13">
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13">
         <v>40</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:14">
+    <row r="14" ht="24" customHeight="1" spans="1:15">
       <c r="A14">
         <v>22006</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1686,33 +1758,36 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>4</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L14">
+      <c r="K14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14">
         <v>40</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" ht="28" spans="1:14">
+    <row r="15" ht="56" spans="1:15">
       <c r="A15">
         <v>22007</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1724,33 +1799,36 @@
         <v>0</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>1</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L15">
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15">
         <v>40</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>9</v>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1" spans="1:14">
+    <row r="16" ht="33" customHeight="1" spans="1:15">
       <c r="A16">
         <v>22008</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1762,10 +1840,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1773,22 +1851,25 @@
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16">
         <v>40</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>13</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:14">
+    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:15">
       <c r="A17" s="1">
         <v>23001</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -1800,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1811,14 +1892,169 @@
       <c r="I17" s="1">
         <v>0</v>
       </c>
-      <c r="J17" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17" s="1">
         <v>100</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18">
+        <v>21801</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19">
+        <v>21802</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20">
+        <v>21803</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21">
+        <v>21804</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
   <si>
     <t>id</t>
   </si>
@@ -85,136 +85,136 @@
     <t>卡牌介绍占坑</t>
   </si>
   <si>
+    <t>萌发新芽</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生枝{made}，也就是下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>shake(1,0.2)</t>
+  </si>
+  <si>
+    <t>丛生之态</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生长{added}</t>
+  </si>
+  <si>
+    <t>去芜存菁</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，本回合随机获得一张罕见礼物卡</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,1,2);magnify(0.2)</t>
+  </si>
+  <si>
+    <t>刈除侧蔓</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的属性三提升30点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(30,2)</t>
+  </si>
+  <si>
+    <t>修枝整形</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的的属性一提升{nature1}点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(50,1)</t>
+  </si>
+  <si>
+    <t>光合积累</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生长，将卡中数值不足12的部分加成到12</t>
+  </si>
+  <si>
+    <t>beAddedTo(12);shake(1,0.2)</t>
+  </si>
+  <si>
+    <t>枝条分叉</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生枝{made}，下回合获得你生枝的牌</t>
+  </si>
+  <si>
+    <t>幼枝初展</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生枝{made}，本回合随机获得一张普通属性卡</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,1,1);shake(1,0.2)</t>
+  </si>
+  <si>
+    <t>截干蓄势</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
+  </si>
+  <si>
+    <t>拔节有声</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若卡组中有三个以上相同的礼物，生长40，否则生长5</t>
+  </si>
+  <si>
+    <t>addWithSame(3,40,5);magnify(0.3)</t>
+  </si>
+  <si>
+    <t>凭空</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若手中没有礼物牌，则随机获得一个罕见礼物卡</t>
+  </si>
+  <si>
+    <t>addRandomCardIfNot(1,1,2)</t>
+  </si>
+  <si>
+    <t>春来发枝</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生长{added}，此牌生长的数值提升4</t>
+  </si>
+  <si>
+    <t>addAddNum(4);magnify(0.2)</t>
+  </si>
+  <si>
+    <t>整冠截顶</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
+  </si>
+  <si>
+    <t>addNatureAtSumIf(40,1);shake(1,0.3)</t>
+  </si>
+  <si>
+    <t>一叶知秋</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 将手牌中的所有礼物都变成同一个随机礼物</t>
+  </si>
+  <si>
+    <t>changeHandGift()</t>
+  </si>
+  <si>
+    <t>移花接木</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 若卡组中有6个以上相同的礼物，生长所有相同的礼物80</t>
+  </si>
+  <si>
+    <t>addWIthSameTogether(6,80);magnify(0.5)</t>
+  </si>
+  <si>
+    <t>测试卡牌</t>
+  </si>
+  <si>
     <t>beMade(2)</t>
-  </si>
-  <si>
-    <t>萌发新芽</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生枝{made}，也就是下回合获得你生枝的牌</t>
-  </si>
-  <si>
-    <t>shake(1,0.2)</t>
-  </si>
-  <si>
-    <t>丛生之态</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生长{added}</t>
-  </si>
-  <si>
-    <t>去芜存菁</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，本回合随机获得一张罕见礼物卡</t>
-  </si>
-  <si>
-    <t>addRandomCard(1,1,2);magnify(0.2)</t>
-  </si>
-  <si>
-    <t>刈除侧蔓</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的属性三提升30点</t>
-  </si>
-  <si>
-    <t>addNatureAtSum(30,2)</t>
-  </si>
-  <si>
-    <t>修枝整形</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的的属性一提升{nature1}点</t>
-  </si>
-  <si>
-    <t>addNatureAtSum(50,1)</t>
-  </si>
-  <si>
-    <t>光合积累</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生长，将卡中数值不足12的部分加成到12</t>
-  </si>
-  <si>
-    <t>beAddedTo(12);shake(1,0.2)</t>
-  </si>
-  <si>
-    <t>枝条分叉</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生枝{made}，下回合获得你生枝的牌</t>
-  </si>
-  <si>
-    <t>幼枝初展</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生枝{made}，本回合随机获得一张普通属性卡</t>
-  </si>
-  <si>
-    <t>addRandomCard(1,1,1);shake(1,0.2)</t>
-  </si>
-  <si>
-    <t>截干蓄势</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
-  </si>
-  <si>
-    <t>拔节有声</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若卡组中有三个以上相同的礼物，生长40，否则生长5</t>
-  </si>
-  <si>
-    <t>addWithSame(3,40,5);magnify(0.3)</t>
-  </si>
-  <si>
-    <t>凭空</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若手中没有礼物牌，则随机获得一个罕见礼物卡</t>
-  </si>
-  <si>
-    <t>addRandomCardIfNot(1,1,2)</t>
-  </si>
-  <si>
-    <t>春来发枝</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生长{added}，此牌生长的数值提升4</t>
-  </si>
-  <si>
-    <t>addAddNum(4);magnify(0.2)</t>
-  </si>
-  <si>
-    <t>整冠截顶</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
-  </si>
-  <si>
-    <t>addNatureAtSumIf(40,1);shake(1,0.3)</t>
-  </si>
-  <si>
-    <t>一叶知秋</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 将手牌中的所有礼物都变成同一个随机礼物</t>
-  </si>
-  <si>
-    <t>changeHandGift()</t>
-  </si>
-  <si>
-    <t>移花接木</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 若卡组中有6个以上相同的礼物，生长所有相同的礼物80</t>
-  </si>
-  <si>
-    <t>addWIthSameTogether(6,80);magnify(0.5)</t>
-  </si>
-  <si>
-    <t>测试卡牌</t>
   </si>
   <si>
     <t>beMade(3)</t>
@@ -1279,7 +1279,7 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1287,9 +1287,7 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="K2" s="4"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="O2">
@@ -1301,19 +1299,19 @@
         <v>21001</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
@@ -1328,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>20</v>
@@ -1342,19 +1340,19 @@
         <v>21002</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -1380,19 +1378,19 @@
         <v>21003</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>17</v>
@@ -1407,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M5">
         <v>20</v>
@@ -1421,19 +1419,19 @@
         <v>21004</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
@@ -1448,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M6">
         <v>20</v>
@@ -1462,7 +1460,7 @@
         <v>21005</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -1474,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
@@ -1489,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M7">
         <v>20</v>
@@ -1503,19 +1501,19 @@
         <v>21006</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -1530,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M8">
         <v>20</v>
@@ -1544,19 +1542,19 @@
         <v>22001</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>17</v>
@@ -1582,19 +1580,19 @@
         <v>22002</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>17</v>
@@ -1609,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M10">
         <v>40</v>
@@ -1623,7 +1621,7 @@
         <v>22003</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1635,7 +1633,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>17</v>
@@ -1650,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M11">
         <v>40</v>
@@ -1664,19 +1662,19 @@
         <v>22004</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>17</v>
@@ -1691,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M12">
         <v>40</v>
@@ -1705,19 +1703,19 @@
         <v>22005</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>17</v>
@@ -1732,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M13">
         <v>40</v>
@@ -1746,19 +1744,19 @@
         <v>22006</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>17</v>
@@ -1773,7 +1771,7 @@
         <v>4</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M14">
         <v>40</v>
@@ -1787,19 +1785,19 @@
         <v>22007</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
@@ -1814,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M15">
         <v>40</v>
@@ -1828,19 +1826,19 @@
         <v>22008</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>17</v>
@@ -1855,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M16">
         <v>40</v>
@@ -1869,19 +1867,19 @@
         <v>23001</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>59</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>17</v>
@@ -1896,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M17" s="1">
         <v>100</v>
@@ -1910,19 +1908,19 @@
         <v>21801</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>17</v>
@@ -1937,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -1948,7 +1946,7 @@
         <v>21802</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1986,7 +1984,7 @@
         <v>21803</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -2024,7 +2022,7 @@
         <v>21804</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21">
         <v>3</v>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>id</t>
   </si>
@@ -52,6 +52,9 @@
     <t>text</t>
   </si>
   <si>
+    <t>prompt</t>
+  </si>
+  <si>
     <t>made</t>
   </si>
   <si>
@@ -79,7 +82,7 @@
     <t>初始功能牌</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生枝{made}</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 制造{made}</t>
   </si>
   <si>
     <t>卡牌介绍占坑</t>
@@ -88,7 +91,7 @@
     <t>萌发新芽</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生枝{made}，也就是下回合获得你生枝的牌</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 制造{made}，也就是下回合获得你制造的牌</t>
   </si>
   <si>
     <t>shake(1,0.2)</t>
@@ -97,13 +100,13 @@
     <t>丛生之态</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生长{added}</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化{added}</t>
   </si>
   <si>
     <t>去芜存菁</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，本回合随机获得一张罕见礼物卡</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，本回合随机获得一张罕见礼物卡</t>
   </si>
   <si>
     <t>addRandomCard(1,1,2);magnify(0.2)</t>
@@ -112,7 +115,7 @@
     <t>刈除侧蔓</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的属性三提升30点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，蒂娜的属性三提升30点</t>
   </si>
   <si>
     <t>addNatureAtSum(30,2)</t>
@@ -121,7 +124,7 @@
     <t>修枝整形</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的的属性一提升{nature1}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，蒂娜的的属性一提升{nature1}点</t>
   </si>
   <si>
     <t>addNatureAtSum(50,1)</t>
@@ -130,7 +133,7 @@
     <t>光合积累</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 生长，将卡中数值不足12的部分加成到12</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化，将卡中数值不足12的部分加成到12</t>
   </si>
   <si>
     <t>beAddedTo(12);shake(1,0.2)</t>
@@ -139,13 +142,13 @@
     <t>枝条分叉</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生枝{made}，下回合获得你生枝的牌</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 制造{made}，下回合获得你制造的牌</t>
   </si>
   <si>
     <t>幼枝初展</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生枝{made}，本回合随机获得一张普通属性卡</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 制造{made}，本回合随机获得一张普通属性卡</t>
   </si>
   <si>
     <t>addRandomCard(1,1,1);shake(1,0.2)</t>
@@ -154,13 +157,13 @@
     <t>截干蓄势</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
   </si>
   <si>
     <t>拔节有声</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若卡组中有三个以上相同的礼物，生长40，否则生长5</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若卡组中有三个以上相同的礼物，美化40，否则美化5</t>
   </si>
   <si>
     <t>addWithSame(3,40,5);magnify(0.3)</t>
@@ -178,7 +181,7 @@
     <t>春来发枝</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 生长{added}，此牌生长的数值提升4</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 美化{added}，此牌美化的数值提升4</t>
   </si>
   <si>
     <t>addAddNum(4);magnify(0.2)</t>
@@ -187,7 +190,7 @@
     <t>整冠截顶</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 剪枝{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
   </si>
   <si>
     <t>addNatureAtSumIf(40,1);shake(1,0.3)</t>
@@ -205,7 +208,7 @@
     <t>移花接木</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 若卡组中有6个以上相同的礼物，生长所有相同的礼物80</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 若卡组中有6个以上相同的礼物，美化所有相同的礼物80</t>
   </si>
   <si>
     <t>addWIthSameTogether(6,80);magnify(0.5)</t>
@@ -214,16 +217,19 @@
     <t>测试卡牌</t>
   </si>
   <si>
-    <t>beMade(2)</t>
-  </si>
-  <si>
-    <t>beMade(3)</t>
-  </si>
-  <si>
-    <t>beMade(4)</t>
-  </si>
-  <si>
-    <t>beMade(5)</t>
+    <t>addWithSame(1,10,5)</t>
+  </si>
+  <si>
+    <t>addWithSame(2,10,5)</t>
+  </si>
+  <si>
+    <t>addWIthSameTogether(2,80);</t>
+  </si>
+  <si>
+    <t>addWIthSameTogether(2,80);magnify(0.5)</t>
+  </si>
+  <si>
+    <t>addNatureAtSumIf(1,2,88)</t>
   </si>
 </sst>
 </file>
@@ -1196,20 +1202,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
     <col min="6" max="6" width="31.5454545454545" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.9090909090909" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.9090909090909" customWidth="1"/>
-    <col min="11" max="11" width="16.1818181818182" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.8181818181818" customWidth="1"/>
-    <col min="13" max="13" width="11.7272727272727" customWidth="1"/>
-    <col min="14" max="14" width="19.3636363636364" customWidth="1"/>
+    <col min="11" max="11" width="11.9090909090909" customWidth="1"/>
+    <col min="12" max="12" width="16.1818181818182" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.8181818181818" customWidth="1"/>
+    <col min="14" max="14" width="11.7272727272727" customWidth="1"/>
+    <col min="15" max="15" width="19.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1240,28 +1246,31 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" ht="28" spans="1:15">
+    <row r="2" ht="28" spans="1:16">
       <c r="A2" s="3">
         <v>21601</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -1273,74 +1282,77 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="3"/>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4"/>
       <c r="M2" s="3"/>
-      <c r="O2">
+      <c r="N2" s="3"/>
+      <c r="P2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="42" spans="1:15">
+    <row r="3" ht="42" spans="1:16">
       <c r="A3">
         <v>21001</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3">
         <v>20</v>
       </c>
-      <c r="M3">
-        <v>20</v>
-      </c>
-      <c r="O3">
+      <c r="P3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:15">
+    <row r="4" ht="20" customHeight="1" spans="1:16">
       <c r="A4">
         <v>21002</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1352,33 +1364,33 @@
         <v>0</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>4</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>20</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="27" customHeight="1" spans="1:15">
+    <row r="5" ht="27" customHeight="1" spans="1:16">
       <c r="A5">
         <v>21003</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1390,36 +1402,36 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5">
         <v>20</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="42" spans="1:15">
+    <row r="6" ht="42" spans="1:16">
       <c r="A6">
         <v>21004</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1431,36 +1443,36 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6">
         <v>20</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:15">
+    <row r="7" ht="42" spans="1:16">
       <c r="A7">
         <v>21005</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -1472,36 +1484,36 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>2</v>
       </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7">
         <v>20</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" spans="1:15">
+    <row r="8" ht="30" customHeight="1" spans="1:16">
       <c r="A8">
         <v>21006</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1513,13 +1525,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1527,22 +1536,25 @@
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8">
         <v>20</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="27" customHeight="1" spans="1:15">
+    <row r="9" ht="27" customHeight="1" spans="1:16">
       <c r="A9">
         <v>22001</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1554,33 +1566,33 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9">
+        <v>18</v>
+      </c>
+      <c r="I9">
         <v>3</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="M9">
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="N9">
         <v>40</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" ht="51" customHeight="1" spans="1:15">
+    <row r="10" ht="51" customHeight="1" spans="1:16">
       <c r="A10">
         <v>22002</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1592,36 +1604,36 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10">
+        <v>18</v>
+      </c>
+      <c r="I10">
         <v>1</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10">
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O10">
+      <c r="N10">
+        <v>40</v>
+      </c>
+      <c r="P10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="27" customHeight="1" spans="1:15">
+    <row r="11" ht="27" customHeight="1" spans="1:16">
       <c r="A11">
         <v>22003</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1633,36 +1645,36 @@
         <v>100</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>5</v>
       </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11">
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11">
         <v>40</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1" spans="1:15">
+    <row r="12" ht="38" customHeight="1" spans="1:16">
       <c r="A12">
         <v>22004</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1674,13 +1686,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1688,22 +1697,25 @@
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M12">
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12">
         <v>40</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="29" customHeight="1" spans="1:15">
+    <row r="13" ht="29" customHeight="1" spans="1:16">
       <c r="A13">
         <v>22005</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1715,13 +1727,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1729,22 +1738,25 @@
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M13">
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13">
         <v>40</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:15">
+    <row r="14" ht="24" customHeight="1" spans="1:16">
       <c r="A14">
         <v>22006</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1756,36 +1768,36 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>4</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14">
         <v>40</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" ht="56" spans="1:15">
+    <row r="15" ht="56" spans="1:16">
       <c r="A15">
         <v>22007</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1797,36 +1809,36 @@
         <v>0</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
         <v>1</v>
       </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M15">
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15">
         <v>40</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>9</v>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1" spans="1:15">
+    <row r="16" ht="33" customHeight="1" spans="1:16">
       <c r="A16">
         <v>22008</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1838,13 +1850,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1852,22 +1861,25 @@
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M16">
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16">
         <v>40</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>13</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:15">
+    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:16">
       <c r="A17" s="1">
         <v>23001</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -1879,13 +1891,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -1893,22 +1902,25 @@
       <c r="J17" s="1">
         <v>0</v>
       </c>
-      <c r="K17" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="M17" s="1">
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="1">
         <v>100</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" ht="28" spans="1:16">
       <c r="A18">
-        <v>21801</v>
+        <v>22801</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1920,33 +1932,33 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="42" spans="1:16">
+      <c r="A19">
+        <v>22802</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19">
-        <v>21802</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1958,13 +1970,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1972,19 +1981,22 @@
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M19">
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" ht="28" spans="1:16">
       <c r="A20">
-        <v>21803</v>
+        <v>22803</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -1996,13 +2008,10 @@
         <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2010,19 +2019,22 @@
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M20">
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" ht="28" spans="1:16">
       <c r="A21">
-        <v>21804</v>
+        <v>22804</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2034,13 +2046,10 @@
         <v>3</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2048,10 +2057,13 @@
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="M21">
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N21">
         <v>0</v>
       </c>
     </row>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -1328,6 +1328,9 @@
       <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
       <c r="I3">
         <v>1</v>
       </c>
@@ -1369,6 +1372,9 @@
       <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
       <c r="I4">
         <v>0</v>
       </c>
@@ -1407,6 +1413,9 @@
       <c r="G5" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
       <c r="I5">
         <v>0</v>
       </c>
@@ -1448,6 +1457,9 @@
       <c r="G6" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
       <c r="I6">
         <v>0</v>
       </c>
@@ -1489,6 +1501,9 @@
       <c r="G7" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
       <c r="I7">
         <v>0</v>
       </c>
@@ -1530,6 +1545,9 @@
       <c r="G8" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
       <c r="I8">
         <v>0</v>
       </c>
@@ -1571,6 +1589,9 @@
       <c r="G9" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
       <c r="I9">
         <v>3</v>
       </c>
@@ -1609,6 +1630,9 @@
       <c r="G10" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
       <c r="I10">
         <v>1</v>
       </c>
@@ -1650,6 +1674,9 @@
       <c r="G11" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
       <c r="I11">
         <v>0</v>
       </c>
@@ -1691,6 +1718,9 @@
       <c r="G12" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
       <c r="I12">
         <v>0</v>
       </c>
@@ -1732,6 +1762,9 @@
       <c r="G13" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
       <c r="I13">
         <v>0</v>
       </c>
@@ -1773,6 +1806,9 @@
       <c r="G14" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
       <c r="I14">
         <v>0</v>
       </c>
@@ -1814,6 +1850,9 @@
       <c r="G15" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
       <c r="I15">
         <v>0</v>
       </c>
@@ -1855,6 +1894,9 @@
       <c r="G16" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H16">
+        <v>4</v>
+      </c>
       <c r="I16">
         <v>0</v>
       </c>
@@ -1896,6 +1938,9 @@
       <c r="G17" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
@@ -1937,6 +1982,9 @@
       <c r="G18" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -1975,6 +2023,9 @@
       <c r="G19" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H19">
+        <v>4</v>
+      </c>
       <c r="I19">
         <v>0</v>
       </c>
@@ -2013,6 +2064,9 @@
       <c r="G20" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
       <c r="I20">
         <v>0</v>
       </c>
@@ -2050,6 +2104,9 @@
       </c>
       <c r="G21" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
       </c>
       <c r="I21">
         <v>0</v>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
   <si>
     <t>id</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>sale</t>
+  </si>
+  <si>
+    <t>sell</t>
   </si>
   <si>
     <t>nextTurn</t>
@@ -1202,7 +1205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
@@ -1212,10 +1215,10 @@
     <col min="12" max="12" width="16.1818181818182" style="2" customWidth="1"/>
     <col min="13" max="13" width="10.8181818181818" customWidth="1"/>
     <col min="14" max="14" width="11.7272727272727" customWidth="1"/>
-    <col min="15" max="15" width="19.3636363636364" customWidth="1"/>
+    <col min="16" max="16" width="19.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1264,13 +1267,16 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" ht="28" spans="1:16">
+    <row r="2" ht="28" spans="1:17">
       <c r="A2" s="3">
         <v>21601</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -1282,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1302,31 +1308,34 @@
       <c r="L2" s="4"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="P2">
+      <c r="O2">
+        <v>10</v>
+      </c>
+      <c r="Q2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="42" spans="1:16">
+    <row r="3" ht="42" spans="1:17">
       <c r="A3">
         <v>21001</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1341,21 +1350,24 @@
         <v>0</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3">
         <v>20</v>
       </c>
-      <c r="P3">
+      <c r="O3">
+        <v>10</v>
+      </c>
+      <c r="Q3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:16">
+    <row r="4" ht="20" customHeight="1" spans="1:17">
       <c r="A4">
         <v>21002</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1367,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1387,16 +1399,19 @@
       <c r="N4">
         <v>20</v>
       </c>
-      <c r="P4">
+      <c r="O4">
+        <v>10</v>
+      </c>
+      <c r="Q4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="27" customHeight="1" spans="1:16">
+    <row r="5" ht="27" customHeight="1" spans="1:17">
       <c r="A5">
         <v>21003</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1408,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -1426,21 +1441,24 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N5">
         <v>20</v>
       </c>
-      <c r="P5">
+      <c r="O5">
+        <v>10</v>
+      </c>
+      <c r="Q5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="42" spans="1:16">
+    <row r="6" ht="42" spans="1:17">
       <c r="A6">
         <v>21004</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1452,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -1470,21 +1488,24 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
-      <c r="P6">
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="Q6">
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:16">
+    <row r="7" ht="42" spans="1:17">
       <c r="A7">
         <v>21005</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -1496,10 +1517,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -1514,21 +1535,24 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N7">
         <v>20</v>
       </c>
-      <c r="P7">
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="Q7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" spans="1:16">
+    <row r="8" ht="30" customHeight="1" spans="1:17">
       <c r="A8">
         <v>21006</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1540,10 +1564,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H8">
         <v>3</v>
@@ -1558,21 +1582,24 @@
         <v>0</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N8">
         <v>20</v>
       </c>
-      <c r="P8">
+      <c r="O8">
+        <v>10</v>
+      </c>
+      <c r="Q8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="27" customHeight="1" spans="1:16">
+    <row r="9" ht="27" customHeight="1" spans="1:17">
       <c r="A9">
         <v>22001</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1584,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1604,16 +1631,19 @@
       <c r="N9">
         <v>40</v>
       </c>
-      <c r="P9">
+      <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="Q9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" ht="51" customHeight="1" spans="1:16">
+    <row r="10" ht="51" customHeight="1" spans="1:17">
       <c r="A10">
         <v>22002</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1625,10 +1655,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1643,21 +1673,24 @@
         <v>0</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N10">
         <v>40</v>
       </c>
-      <c r="P10">
+      <c r="O10">
+        <v>10</v>
+      </c>
+      <c r="Q10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="27" customHeight="1" spans="1:16">
+    <row r="11" ht="27" customHeight="1" spans="1:17">
       <c r="A11">
         <v>22003</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1669,10 +1702,10 @@
         <v>100</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11">
         <v>4</v>
@@ -1687,21 +1720,24 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11">
         <v>40</v>
       </c>
-      <c r="P11">
+      <c r="O11">
+        <v>10</v>
+      </c>
+      <c r="Q11">
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1" spans="1:16">
+    <row r="12" ht="38" customHeight="1" spans="1:17">
       <c r="A12">
         <v>22004</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1713,10 +1749,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12">
         <v>4</v>
@@ -1731,21 +1767,24 @@
         <v>0</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N12">
         <v>40</v>
       </c>
-      <c r="P12">
+      <c r="O12">
+        <v>10</v>
+      </c>
+      <c r="Q12">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="29" customHeight="1" spans="1:16">
+    <row r="13" ht="29" customHeight="1" spans="1:17">
       <c r="A13">
         <v>22005</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1757,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H13">
         <v>4</v>
@@ -1775,21 +1814,24 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N13">
         <v>40</v>
       </c>
-      <c r="P13">
+      <c r="O13">
+        <v>10</v>
+      </c>
+      <c r="Q13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:16">
+    <row r="14" ht="24" customHeight="1" spans="1:17">
       <c r="A14">
         <v>22006</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1801,10 +1843,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -1819,21 +1861,24 @@
         <v>4</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N14">
         <v>40</v>
       </c>
-      <c r="P14">
+      <c r="O14">
+        <v>10</v>
+      </c>
+      <c r="Q14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" ht="56" spans="1:16">
+    <row r="15" ht="56" spans="1:17">
       <c r="A15">
         <v>22007</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1845,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H15">
         <v>4</v>
@@ -1863,21 +1908,24 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N15">
         <v>40</v>
       </c>
-      <c r="P15">
+      <c r="O15">
+        <v>10</v>
+      </c>
+      <c r="Q15">
         <v>9</v>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1" spans="1:16">
+    <row r="16" ht="33" customHeight="1" spans="1:17">
       <c r="A16">
         <v>22008</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1889,10 +1937,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H16">
         <v>4</v>
@@ -1907,21 +1955,24 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N16">
         <v>40</v>
       </c>
-      <c r="P16">
+      <c r="O16">
+        <v>10</v>
+      </c>
+      <c r="Q16">
         <v>13</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:16">
+    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:17">
       <c r="A17" s="1">
         <v>23001</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -1933,10 +1984,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -1951,21 +2002,24 @@
         <v>0</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N17" s="1">
         <v>100</v>
       </c>
-      <c r="P17">
+      <c r="O17">
+        <v>10</v>
+      </c>
+      <c r="Q17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" ht="28" spans="1:16">
+    <row r="18" ht="28" spans="1:17">
       <c r="A18">
         <v>22801</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1977,10 +2031,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18">
         <v>4</v>
@@ -1995,18 +2049,21 @@
         <v>0</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
+      <c r="O18">
+        <v>10</v>
+      </c>
     </row>
-    <row r="19" ht="42" spans="1:16">
+    <row r="19" ht="42" spans="1:17">
       <c r="A19">
         <v>22802</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2018,10 +2075,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19">
         <v>4</v>
@@ -2036,18 +2093,21 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N19">
         <v>0</v>
       </c>
+      <c r="O19">
+        <v>10</v>
+      </c>
     </row>
-    <row r="20" ht="28" spans="1:16">
+    <row r="20" ht="28" spans="1:17">
       <c r="A20">
         <v>22803</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -2059,10 +2119,10 @@
         <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -2077,18 +2137,21 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
+      <c r="O20">
+        <v>10</v>
+      </c>
     </row>
-    <row r="21" ht="28" spans="1:16">
+    <row r="21" ht="28" spans="1:17">
       <c r="A21">
         <v>22804</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2100,10 +2163,10 @@
         <v>3</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -2118,10 +2181,13 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N21">
         <v>0</v>
+      </c>
+      <c r="O21">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="76">
   <si>
     <t>id</t>
   </si>
@@ -85,7 +85,7 @@
     <t>初始功能牌</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 制造{made}</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化{added}</t>
   </si>
   <si>
     <t>卡牌介绍占坑</t>
@@ -103,9 +103,6 @@
     <t>丛生之态</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化{added}</t>
-  </si>
-  <si>
     <t>去芜存菁</t>
   </si>
   <si>
@@ -118,10 +115,10 @@
     <t>刈除侧蔓</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，蒂娜的属性三提升30点</t>
-  </si>
-  <si>
-    <t>addNatureAtSum(30,2)</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，蒂娜的属性三提升34点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(34,2)</t>
   </si>
   <si>
     <t>修枝整形</t>
@@ -130,16 +127,13 @@
     <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，蒂娜的的属性一提升{nature1}点</t>
   </si>
   <si>
-    <t>addNatureAtSum(50,1)</t>
-  </si>
-  <si>
     <t>光合积累</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化，将卡中数值不足12的部分加成到12</t>
-  </si>
-  <si>
-    <t>beAddedTo(12);shake(1,0.2)</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化，将卡中数值不足14的部分加成到14</t>
+  </si>
+  <si>
+    <t>beAddedTo(14);shake(1,0.2)</t>
   </si>
   <si>
     <t>枝条分叉</t>
@@ -166,7 +160,7 @@
     <t>拔节有声</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若卡组中有三个以上相同的礼物，美化40，否则美化5</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若卡组中有三个以上相同的礼物，美化40，否则美化6</t>
   </si>
   <si>
     <t>addWithSame(3,40,5);magnify(0.3)</t>
@@ -175,10 +169,10 @@
     <t>凭空</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若手中没有礼物牌，则随机获得一个罕见礼物卡</t>
-  </si>
-  <si>
-    <t>addRandomCardIfNot(1,1,2)</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若手中没有礼物牌，则随机获得两个罕见礼物卡</t>
+  </si>
+  <si>
+    <t>addRandomCardIfNot(1,2,2)</t>
   </si>
   <si>
     <t>春来发枝</t>
@@ -208,6 +202,15 @@
     <t>changeHandGift()</t>
   </si>
   <si>
+    <t>提取</t>
+  </si>
+  <si>
+    <t>从工具袋中取出2个物品</t>
+  </si>
+  <si>
+    <t>drawCard(2)</t>
+  </si>
+  <si>
     <t>移花接木</t>
   </si>
   <si>
@@ -217,22 +220,43 @@
     <t>addWIthSameTogether(6,80);magnify(0.5)</t>
   </si>
   <si>
-    <t>测试卡牌</t>
-  </si>
-  <si>
-    <t>addWithSame(1,10,5)</t>
-  </si>
-  <si>
-    <t>addWithSame(2,10,5)</t>
-  </si>
-  <si>
-    <t>addWIthSameTogether(2,80);</t>
-  </si>
-  <si>
-    <t>addWIthSameTogether(2,80);magnify(0.5)</t>
-  </si>
-  <si>
-    <t>addNatureAtSumIf(1,2,88)</t>
+    <t>抓取</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 从袋子里取出6个物品</t>
+  </si>
+  <si>
+    <t>drawCard(6)</t>
+  </si>
+  <si>
+    <t>大包装</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  美化{added}</t>
+  </si>
+  <si>
+    <t>预支未来</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 下回合属性加成提升到2倍</t>
+  </si>
+  <si>
+    <t>changeProperty(2)</t>
+  </si>
+  <si>
+    <t>超级拼装</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 制造{made}</t>
+  </si>
+  <si>
+    <t>大盲盒</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 随机获得3张罕见礼物牌</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,2,3)</t>
   </si>
 </sst>
 </file>
@@ -245,7 +269,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,6 +282,19 @@
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -404,12 +441,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -730,137 +785,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -885,13 +940,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1205,12 +1278,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
     <col min="6" max="6" width="31.5454545454545" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.9090909090909" style="2" customWidth="1"/>
+    <col min="8" max="8" width="5.72727272727273" customWidth="1"/>
     <col min="11" max="11" width="11.9090909090909" customWidth="1"/>
     <col min="12" max="12" width="16.1818181818182" style="2" customWidth="1"/>
     <col min="13" max="13" width="10.8181818181818" customWidth="1"/>
@@ -1294,20 +1368,22 @@
         <v>19</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="N2" s="3">
+        <v>10</v>
+      </c>
       <c r="O2">
         <v>10</v>
       </c>
@@ -1379,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>19</v>
@@ -1394,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>20</v>
@@ -1411,19 +1487,19 @@
         <v>21003</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>19</v>
@@ -1441,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N5">
         <v>20</v>
@@ -1458,19 +1534,19 @@
         <v>21004</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>19</v>
@@ -1488,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N6">
         <v>20</v>
@@ -1505,19 +1581,19 @@
         <v>21005</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>19</v>
@@ -1534,9 +1610,7 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="L7" s="2"/>
       <c r="N7">
         <v>20</v>
       </c>
@@ -1552,7 +1626,7 @@
         <v>21006</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1564,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>19</v>
@@ -1582,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N8">
         <v>20</v>
@@ -1595,11 +1669,11 @@
       </c>
     </row>
     <row r="9" ht="27" customHeight="1" spans="1:17">
-      <c r="A9">
+      <c r="A9" s="8">
         <v>22001</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1611,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>19</v>
@@ -1639,11 +1713,11 @@
       </c>
     </row>
     <row r="10" ht="51" customHeight="1" spans="1:17">
-      <c r="A10">
+      <c r="A10" s="9">
         <v>22002</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1655,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>19</v>
@@ -1664,7 +1738,7 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1673,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N10">
         <v>40</v>
@@ -1686,23 +1760,23 @@
       </c>
     </row>
     <row r="11" ht="27" customHeight="1" spans="1:17">
-      <c r="A11">
+      <c r="A11" s="9">
         <v>22003</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>19</v>
@@ -1733,11 +1807,11 @@
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:17">
-      <c r="A12">
+      <c r="A12" s="9">
         <v>22004</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1749,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>19</v>
@@ -1767,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N12">
         <v>40</v>
@@ -1780,11 +1854,11 @@
       </c>
     </row>
     <row r="13" ht="29" customHeight="1" spans="1:17">
-      <c r="A13">
+      <c r="A13" s="9">
         <v>22005</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1796,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>19</v>
@@ -1814,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N13">
         <v>40</v>
@@ -1827,11 +1901,11 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:17">
-      <c r="A14">
+      <c r="A14" s="9">
         <v>22006</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1843,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>19</v>
@@ -1858,10 +1932,10 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N14">
         <v>40</v>
@@ -1874,11 +1948,11 @@
       </c>
     </row>
     <row r="15" ht="56" spans="1:17">
-      <c r="A15">
+      <c r="A15" s="9">
         <v>22007</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1890,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>19</v>
@@ -1908,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N15">
         <v>40</v>
@@ -1921,11 +1995,11 @@
       </c>
     </row>
     <row r="16" ht="33" customHeight="1" spans="1:17">
-      <c r="A16">
+      <c r="A16" s="9">
         <v>22008</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>56</v>
+      <c r="B16" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1937,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>19</v>
@@ -1955,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N16">
         <v>40</v>
@@ -1968,70 +2042,52 @@
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:17">
-      <c r="A17" s="1">
+      <c r="A17" s="8">
+        <v>22009</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17"/>
+      <c r="L17" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="O17"/>
+      <c r="Q17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="36" customHeight="1" spans="1:17">
+      <c r="A18" s="1">
         <v>23001</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17">
-        <v>4</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="10" t="s">
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="N17" s="1">
-        <v>100</v>
-      </c>
-      <c r="O17">
-        <v>10</v>
-      </c>
-      <c r="Q17">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" ht="28" spans="1:17">
-      <c r="A18">
-        <v>22801</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>19</v>
@@ -2039,155 +2095,139 @@
       <c r="H18">
         <v>4</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="1">
+        <v>100</v>
       </c>
       <c r="O18">
         <v>10</v>
       </c>
+      <c r="Q18">
+        <v>15</v>
+      </c>
     </row>
-    <row r="19" ht="42" spans="1:17">
-      <c r="A19">
-        <v>22802</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>62</v>
+    <row r="19" customFormat="1" ht="23" customHeight="1" spans="1:17">
+      <c r="A19" s="14">
+        <v>23002</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19">
-        <v>4</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>10</v>
-      </c>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
     </row>
     <row r="20" ht="28" spans="1:17">
-      <c r="A20">
-        <v>22803</v>
+      <c r="A20" s="14">
+        <v>23003</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="H20">
-        <v>4</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="21" ht="28" spans="1:17">
-      <c r="A21">
-        <v>22804</v>
+    <row r="21" ht="42" spans="1:17">
+      <c r="A21" s="14">
+        <v>23004</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21">
-        <v>4</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>10</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" ht="28" spans="1:17">
+      <c r="A22" s="14">
+        <v>23005</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" ht="42" spans="1:17">
+      <c r="A23" s="14">
+        <v>23006</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="76">
   <si>
     <t>id</t>
   </si>
@@ -205,7 +205,7 @@
     <t>提取</t>
   </si>
   <si>
-    <t>从工具袋中取出2个物品</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 从工具袋中取出2个物品</t>
   </si>
   <si>
     <t>drawCard(2)</t>
@@ -441,7 +441,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -457,18 +457,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -791,7 +779,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -815,16 +803,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
@@ -833,89 +821,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -940,10 +928,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -958,14 +946,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1385,7 +1367,8 @@
         <v>10</v>
       </c>
       <c r="O2">
-        <v>10</v>
+        <f>N2*0.8</f>
+        <v>8</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -1432,7 +1415,8 @@
         <v>20</v>
       </c>
       <c r="O3">
-        <v>10</v>
+        <f t="shared" ref="O3:O16" si="0">N3*0.8</f>
+        <v>16</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1476,7 +1460,8 @@
         <v>20</v>
       </c>
       <c r="O4">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="Q4">
         <v>11</v>
@@ -1486,7 +1471,7 @@
       <c r="A5">
         <v>21003</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C5">
@@ -1523,7 +1508,8 @@
         <v>20</v>
       </c>
       <c r="O5">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -1570,7 +1556,8 @@
         <v>20</v>
       </c>
       <c r="O6">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1610,12 +1597,12 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7" s="2"/>
       <c r="N7">
         <v>20</v>
       </c>
       <c r="O7">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1662,14 +1649,15 @@
         <v>20</v>
       </c>
       <c r="O8">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="Q8">
         <v>7</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1" spans="1:17">
-      <c r="A9" s="8">
+      <c r="A9" s="9">
         <v>22001</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -1706,7 +1694,8 @@
         <v>40</v>
       </c>
       <c r="O9">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1753,7 +1742,8 @@
         <v>40</v>
       </c>
       <c r="O10">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="Q10">
         <v>6</v>
@@ -1800,7 +1790,8 @@
         <v>40</v>
       </c>
       <c r="O11">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="Q11">
         <v>6</v>
@@ -1847,7 +1838,8 @@
         <v>40</v>
       </c>
       <c r="O12">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="Q12">
         <v>7</v>
@@ -1894,7 +1886,8 @@
         <v>40</v>
       </c>
       <c r="O13">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="Q13">
         <v>12</v>
@@ -1941,7 +1934,8 @@
         <v>40</v>
       </c>
       <c r="O14">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -1988,7 +1982,8 @@
         <v>40</v>
       </c>
       <c r="O15">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -2035,14 +2030,15 @@
         <v>40</v>
       </c>
       <c r="O16">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="Q16">
         <v>13</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:17">
-      <c r="A17" s="8">
+      <c r="A17" s="9">
         <v>22009</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -2060,12 +2056,20 @@
       <c r="F17" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="2"/>
+      <c r="G17" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="H17"/>
       <c r="L17" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="O17"/>
+      <c r="N17" s="1">
+        <v>80</v>
+      </c>
+      <c r="O17">
+        <f t="shared" ref="O17:O23" si="1">N17*0.8</f>
+        <v>64</v>
+      </c>
       <c r="Q17">
         <v>8</v>
       </c>
@@ -2108,17 +2112,18 @@
         <v>62</v>
       </c>
       <c r="N18" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O18">
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>64</v>
       </c>
       <c r="Q18">
         <v>15</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="23" customHeight="1" spans="1:17">
-      <c r="A19" s="14">
+      <c r="A19" s="1">
         <v>23002</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -2133,10 +2138,10 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H19">
@@ -2155,12 +2160,17 @@
         <v>65</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+      <c r="N19" s="1">
+        <v>80</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
       <c r="P19" s="2"/>
     </row>
     <row r="20" ht="28" spans="1:17">
-      <c r="A20" s="14">
+      <c r="A20" s="1">
         <v>23003</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2178,56 +2188,123 @@
       <c r="F20" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="G20" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="H20">
         <v>3</v>
       </c>
       <c r="K20">
         <v>28</v>
       </c>
+      <c r="N20" s="1">
+        <v>80</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
     </row>
     <row r="21" ht="42" spans="1:17">
-      <c r="A21" s="14">
+      <c r="A21" s="1">
         <v>23004</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>68</v>
       </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
+      <c r="G21" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="L21" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="N21" s="1">
+        <v>80</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
     </row>
     <row r="22" ht="28" spans="1:17">
-      <c r="A22" s="14">
+      <c r="A22" s="1">
         <v>23005</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
       <c r="F22" s="2" t="s">
         <v>72</v>
       </c>
+      <c r="G22" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22">
         <v>6</v>
       </c>
+      <c r="N22" s="1">
+        <v>80</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
     </row>
     <row r="23" ht="42" spans="1:17">
-      <c r="A23" s="14">
+      <c r="A23" s="1">
         <v>23006</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
       <c r="F23" s="2" t="s">
         <v>74</v>
       </c>
+      <c r="G23" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="L23" s="2" t="s">
         <v>75</v>
+      </c>
+      <c r="N23" s="1">
+        <v>80</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="1"/>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="80">
   <si>
     <t>id</t>
   </si>
@@ -85,7 +85,7 @@
     <t>初始功能牌</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化{added}</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n美化{added}</t>
   </si>
   <si>
     <t>卡牌介绍占坑</t>
@@ -94,7 +94,7 @@
     <t>萌发新芽</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 制造{made}，也就是下回合获得你制造的牌</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 制造{made}，也就是下回合获得你制造的牌</t>
   </si>
   <si>
     <t>shake(1,0.2)</t>
@@ -103,10 +103,13 @@
     <t>丛生之态</t>
   </si>
   <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 美化{added}</t>
+  </si>
+  <si>
     <t>去芜存菁</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，本回合随机获得一张罕见礼物卡</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，本回合随机获得一张罕见礼物卡</t>
   </si>
   <si>
     <t>addRandomCard(1,1,2);magnify(0.2)</t>
@@ -115,7 +118,7 @@
     <t>刈除侧蔓</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，蒂娜的属性三提升34点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，蒂娜的属性三提升34点</t>
   </si>
   <si>
     <t>addNatureAtSum(34,2)</t>
@@ -124,28 +127,37 @@
     <t>修枝整形</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，蒂娜的的属性一提升{nature1}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，蒂娜的的属性一提升{nature1}点</t>
   </si>
   <si>
     <t>光合积累</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化，将卡中数值不足14的部分加成到14</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 美化，将卡中数值不足14的部分加成到14</t>
   </si>
   <si>
     <t>beAddedTo(14);shake(1,0.2)</t>
   </si>
   <si>
+    <t>更新工具</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n制造{made}， 拆卸{broken}</t>
+  </si>
+  <si>
+    <t>1,2,6</t>
+  </si>
+  <si>
     <t>枝条分叉</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 制造{made}，下回合获得你制造的牌</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n制造{made}，下回合获得你制造的牌</t>
   </si>
   <si>
     <t>幼枝初展</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 制造{made}，本回合随机获得一张普通属性卡</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 制造{made}，本回合随机获得一张普通属性卡</t>
   </si>
   <si>
     <t>addRandomCard(1,1,1);shake(1,0.2)</t>
@@ -154,13 +166,13 @@
     <t>截干蓄势</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
   </si>
   <si>
     <t>拔节有声</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若卡组中有三个以上相同的礼物，美化40，否则美化6</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 若卡组中有三个以上相同的礼物，美化40，否则美化6</t>
   </si>
   <si>
     <t>addWithSame(3,40,5);magnify(0.3)</t>
@@ -169,7 +181,7 @@
     <t>凭空</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 若手中没有礼物牌，则随机获得两个罕见礼物卡</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 若手中没有礼物牌，则随机获得两个罕见礼物卡</t>
   </si>
   <si>
     <t>addRandomCardIfNot(1,2,2)</t>
@@ -178,7 +190,7 @@
     <t>春来发枝</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 美化{added}，此牌美化的数值提升4</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 美化{added}，此牌美化的数值提升4</t>
   </si>
   <si>
     <t>addAddNum(4);magnify(0.2)</t>
@@ -187,7 +199,7 @@
     <t>整冠截顶</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 拆卸{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
   </si>
   <si>
     <t>addNatureAtSumIf(40,1);shake(1,0.3)</t>
@@ -196,7 +208,7 @@
     <t>一叶知秋</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 将手牌中的所有礼物都变成同一个随机礼物</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 将手牌中的所有礼物都变成同一个随机礼物</t>
   </si>
   <si>
     <t>changeHandGift()</t>
@@ -205,7 +217,7 @@
     <t>提取</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 从工具袋中取出2个物品</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 从工具袋中取出2个物品</t>
   </si>
   <si>
     <t>drawCard(2)</t>
@@ -214,7 +226,7 @@
     <t>移花接木</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 若卡组中有6个以上相同的礼物，美化所有相同的礼物80</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 若卡组中有6个以上相同的礼物，美化所有相同的礼物80</t>
   </si>
   <si>
     <t>addWIthSameTogether(6,80);magnify(0.5)</t>
@@ -223,7 +235,7 @@
     <t>抓取</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 从袋子里取出6个物品</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 从袋子里取出6个物品</t>
   </si>
   <si>
     <t>drawCard(6)</t>
@@ -232,13 +244,13 @@
     <t>大包装</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  美化{added}</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n  美化{added}</t>
   </si>
   <si>
     <t>预支未来</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 下回合属性加成提升到2倍</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 下回合属性加成提升到2倍</t>
   </si>
   <si>
     <t>changeProperty(2)</t>
@@ -247,13 +259,13 @@
     <t>超级拼装</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 制造{made}</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 制造{made}</t>
   </si>
   <si>
     <t>大盲盒</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 随机获得3张罕见礼物牌</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 随机获得3张罕见礼物牌</t>
   </si>
   <si>
     <t>addRandomCard(1,2,3)</t>
@@ -441,7 +453,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,6 +463,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -779,7 +797,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -803,16 +821,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
@@ -821,89 +839,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -932,6 +950,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1260,7 +1281,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
@@ -1415,7 +1436,7 @@
         <v>20</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O16" si="0">N3*0.8</f>
+        <f>N3*0.8</f>
         <v>16</v>
       </c>
       <c r="Q3">
@@ -1439,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>19</v>
@@ -1460,7 +1481,7 @@
         <v>20</v>
       </c>
       <c r="O4">
-        <f t="shared" si="0"/>
+        <f>N4*0.8</f>
         <v>16</v>
       </c>
       <c r="Q4">
@@ -1472,7 +1493,7 @@
         <v>21003</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1484,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>19</v>
@@ -1502,13 +1523,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N5">
         <v>20</v>
       </c>
       <c r="O5">
-        <f t="shared" si="0"/>
+        <f>N5*0.8</f>
         <v>16</v>
       </c>
       <c r="Q5">
@@ -1520,7 +1541,7 @@
         <v>21004</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1532,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>19</v>
@@ -1550,13 +1571,13 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <f t="shared" si="0"/>
+        <f>N6*0.8</f>
         <v>16</v>
       </c>
       <c r="Q6">
@@ -1568,7 +1589,7 @@
         <v>21005</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -1580,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>19</v>
@@ -1601,7 +1622,7 @@
         <v>20</v>
       </c>
       <c r="O7">
-        <f t="shared" si="0"/>
+        <f>N7*0.8</f>
         <v>16</v>
       </c>
       <c r="Q7">
@@ -1613,7 +1634,7 @@
         <v>21006</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1625,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>19</v>
@@ -1643,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N8">
         <v>20</v>
       </c>
       <c r="O8">
-        <f t="shared" si="0"/>
+        <f>N8*0.8</f>
         <v>16</v>
       </c>
       <c r="Q8">
@@ -1658,10 +1679,10 @@
     </row>
     <row r="9" ht="27" customHeight="1" spans="1:17">
       <c r="A9" s="9">
-        <v>22001</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>35</v>
+        <v>21007</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1673,52 +1694,39 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
         <v>1</v>
       </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="N9">
+    </row>
+    <row r="10" ht="27" customHeight="1" spans="1:17">
+      <c r="A10" s="10">
+        <v>22001</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="Q9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" ht="51" customHeight="1" spans="1:17">
-      <c r="A10" s="9">
-        <v>22002</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>19</v>
@@ -1727,64 +1735,61 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="N10">
         <v>40</v>
       </c>
       <c r="O10">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="O10:O17" si="0">N10*0.8</f>
         <v>32</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="11" ht="27" customHeight="1" spans="1:17">
-      <c r="A11" s="9">
-        <v>22003</v>
+    <row r="11" ht="51" customHeight="1" spans="1:17">
+      <c r="A11" s="10">
+        <v>22002</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="N11">
         <v>40</v>
@@ -1797,24 +1802,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1" spans="1:17">
-      <c r="A12" s="9">
-        <v>22004</v>
+    <row r="12" ht="27" customHeight="1" spans="1:17">
+      <c r="A12" s="10">
+        <v>22003</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>19</v>
@@ -1826,13 +1831,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="N12">
         <v>40</v>
@@ -1842,15 +1847,15 @@
         <v>32</v>
       </c>
       <c r="Q12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="13" ht="29" customHeight="1" spans="1:17">
-      <c r="A13" s="9">
-        <v>22005</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>45</v>
+    <row r="13" ht="38" customHeight="1" spans="1:17">
+      <c r="A13" s="10">
+        <v>22004</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1862,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>19</v>
@@ -1880,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N13">
         <v>40</v>
@@ -1890,15 +1895,15 @@
         <v>32</v>
       </c>
       <c r="Q13">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:17">
-      <c r="A14" s="9">
-        <v>22006</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>48</v>
+    <row r="14" ht="29" customHeight="1" spans="1:17">
+      <c r="A14" s="10">
+        <v>22005</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1910,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>19</v>
@@ -1925,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N14">
         <v>40</v>
@@ -1938,15 +1943,15 @@
         <v>32</v>
       </c>
       <c r="Q14">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="15" ht="56" spans="1:17">
-      <c r="A15" s="9">
-        <v>22007</v>
+    <row r="15" ht="24" customHeight="1" spans="1:17">
+      <c r="A15" s="10">
+        <v>22006</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1958,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>19</v>
@@ -1970,13 +1975,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N15">
         <v>40</v>
@@ -1986,15 +1991,15 @@
         <v>32</v>
       </c>
       <c r="Q15">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1" spans="1:17">
-      <c r="A16" s="9">
-        <v>22008</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>54</v>
+    <row r="16" ht="56" spans="1:17">
+      <c r="A16" s="10">
+        <v>22007</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2006,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>19</v>
@@ -2018,13 +2023,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N16">
         <v>40</v>
@@ -2034,52 +2039,63 @@
         <v>32</v>
       </c>
       <c r="Q16">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="36" customHeight="1" spans="1:17">
-      <c r="A17" s="9">
-        <v>22009</v>
+    <row r="17" ht="33" customHeight="1" spans="1:17">
+      <c r="A17" s="10">
+        <v>22008</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="12" t="s">
         <v>58</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H17"/>
-      <c r="L17" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="N17" s="1">
-        <v>80</v>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17">
+        <v>40</v>
       </c>
       <c r="O17">
-        <f t="shared" ref="O17:O23" si="1">N17*0.8</f>
-        <v>64</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="Q17">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="36" customHeight="1" spans="1:17">
-      <c r="A18" s="1">
-        <v>23001</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>60</v>
+      <c r="A18" s="10">
+        <v>22009</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -2090,76 +2106,64 @@
       <c r="E18" s="1">
         <v>0</v>
       </c>
-      <c r="F18" s="12" t="s">
-        <v>61</v>
+      <c r="F18" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H18">
-        <v>4</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>62</v>
+      <c r="H18"/>
+      <c r="L18" s="14" t="s">
+        <v>63</v>
       </c>
       <c r="N18" s="1">
         <v>80</v>
       </c>
       <c r="O18">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="O18:O24" si="1">N18*0.8</f>
         <v>64</v>
       </c>
       <c r="Q18">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="23" customHeight="1" spans="1:17">
+    <row r="19" s="1" customFormat="1" ht="36" customHeight="1" spans="1:17">
       <c r="A19" s="1">
-        <v>23002</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" s="14" t="s">
+        <v>23001</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>64</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H19">
-        <v>5</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M19" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>66</v>
+      </c>
       <c r="N19" s="1">
         <v>80</v>
       </c>
@@ -2167,14 +2171,16 @@
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="P19" s="2"/>
+      <c r="Q19">
+        <v>15</v>
+      </c>
     </row>
-    <row r="20" ht="28" spans="1:17">
+    <row r="20" customFormat="1" ht="23" customHeight="1" spans="1:17">
       <c r="A20" s="1">
-        <v>23003</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>23002</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2185,18 +2191,28 @@
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>67</v>
+      <c r="F20" s="15" t="s">
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>28</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M20" s="2"/>
       <c r="N20" s="1">
         <v>80</v>
       </c>
@@ -2204,13 +2220,14 @@
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
+      <c r="P20" s="2"/>
     </row>
-    <row r="21" ht="42" spans="1:17">
+    <row r="21" ht="28" spans="1:17">
       <c r="A21" s="1">
-        <v>23004</v>
+        <v>23003</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2222,13 +2239,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>70</v>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <v>28</v>
       </c>
       <c r="N21" s="1">
         <v>80</v>
@@ -2238,12 +2258,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" ht="28" spans="1:17">
+    <row r="22" ht="42" spans="1:17">
       <c r="A22" s="1">
-        <v>23005</v>
+        <v>23004</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2255,16 +2275,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>6</v>
+      <c r="L22" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="N22" s="1">
         <v>80</v>
@@ -2274,12 +2291,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" ht="42" spans="1:17">
+    <row r="23" ht="28" spans="1:17">
       <c r="A23" s="1">
-        <v>23006</v>
+        <v>23005</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2291,18 +2308,54 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>75</v>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>6</v>
       </c>
       <c r="N23" s="1">
         <v>80</v>
       </c>
       <c r="O23">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" ht="42" spans="1:17">
+      <c r="A24" s="1">
+        <v>23006</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N24" s="1">
+        <v>80</v>
+      </c>
+      <c r="O24">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -82,97 +82,130 @@
     <t>dialog</t>
   </si>
   <si>
-    <t>初始功能牌</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n美化{added}</t>
+    <t>漆笔</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化{added}</t>
+  </si>
+  <si>
+    <t>绘制工具，可以让物品更美观</t>
+  </si>
+  <si>
+    <t>DIY小屋零件切割板</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  制造{made}，也就是下回合获得你制造的牌</t>
+  </si>
+  <si>
+    <t>印有精确到毫米的网格和角度，板上的小木条再也不会切歪了。</t>
+  </si>
+  <si>
+    <t>shake(1,0.2)</t>
+  </si>
+  <si>
+    <t>荧光夜光沙</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  美化{added}</t>
+  </si>
+  <si>
+    <t>可以让处理后的物品闪闪发光</t>
+  </si>
+  <si>
+    <t>撬片套装</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，本回合随机获得一张罕见礼物卡</t>
+  </si>
+  <si>
+    <t>塑料制成的各种薄片，可以用来撬动各种物品的外壳</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,1,2);magnify(0.2)</t>
+  </si>
+  <si>
+    <t>管钳扳手</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，蒂娜的属性三提升34点</t>
+  </si>
+  <si>
+    <t>形状奇特的扳手，更易于使用</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(34,2)</t>
+  </si>
+  <si>
+    <t>热风枪</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，蒂娜的的属性一提升{nature1}点</t>
+  </si>
+  <si>
+    <t>能精准吹出高温气流，软化焊点或让不干胶标签完美撕下。</t>
+  </si>
+  <si>
+    <t>马克笔</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  美化，将卡中数值不足14的部分加成到14</t>
+  </si>
+  <si>
+    <t>绘制神器</t>
+  </si>
+  <si>
+    <t>beAddedTo(14);shake(1,0.2)</t>
+  </si>
+  <si>
+    <t>更新工具</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 制造{made}， 拆卸{broken}</t>
   </si>
   <si>
     <t>卡牌介绍占坑</t>
   </si>
   <si>
-    <t>萌发新芽</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 制造{made}，也就是下回合获得你制造的牌</t>
-  </si>
-  <si>
-    <t>shake(1,0.2)</t>
-  </si>
-  <si>
-    <t>丛生之态</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 美化{added}</t>
-  </si>
-  <si>
-    <t>去芜存菁</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，本回合随机获得一张罕见礼物卡</t>
-  </si>
-  <si>
-    <t>addRandomCard(1,1,2);magnify(0.2)</t>
-  </si>
-  <si>
-    <t>刈除侧蔓</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，蒂娜的属性三提升34点</t>
-  </si>
-  <si>
-    <t>addNatureAtSum(34,2)</t>
-  </si>
-  <si>
-    <t>修枝整形</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，蒂娜的的属性一提升{nature1}点</t>
-  </si>
-  <si>
-    <t>光合积累</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n 美化，将卡中数值不足14的部分加成到14</t>
-  </si>
-  <si>
-    <t>beAddedTo(14);shake(1,0.2)</t>
-  </si>
-  <si>
-    <t>更新工具</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;\n制造{made}， 拆卸{broken}</t>
-  </si>
-  <si>
     <t>1,2,6</t>
   </si>
   <si>
-    <t>枝条分叉</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n制造{made}，下回合获得你制造的牌</t>
-  </si>
-  <si>
-    <t>幼枝初展</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 制造{made}，本回合随机获得一张普通属性卡</t>
+    <t>热熔胶枪</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 制造{made}，下回合获得你制造的牌</t>
+  </si>
+  <si>
+    <t>快速粘合小物件的神器</t>
+  </si>
+  <si>
+    <t>金属冲压模具</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  制造{made}，本回合随机获得一张普通属性卡</t>
+  </si>
+  <si>
+    <t>能把薄金属片压出花纹或字母，敲打的声音很有节奏感。</t>
   </si>
   <si>
     <t>addRandomCard(1,1,1);shake(1,0.2)</t>
   </si>
   <si>
-    <t>截干蓄势</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
-  </si>
-  <si>
-    <t>拔节有声</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 若卡组中有三个以上相同的礼物，美化40，否则美化6</t>
+    <t>精密镊子套装</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
+  </si>
+  <si>
+    <t>弯头、直头、平口、尖嘴……拆解细微零件时绝不让它弹飞。</t>
+  </si>
+  <si>
+    <t>彩色电化铝烫印箔</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  若卡组中有三个以上相同的礼物，美化40，否则美化6</t>
+  </si>
+  <si>
+    <t>用加热的铜章压一下，闪亮的镭射图案就会烙印上去</t>
   </si>
   <si>
     <t>addWithSame(3,40,5);magnify(0.3)</t>
@@ -181,7 +214,10 @@
     <t>凭空</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 若手中没有礼物牌，则随机获得两个罕见礼物卡</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  若手中没有礼物牌，则随机获得两个罕见礼物卡</t>
+  </si>
+  <si>
+    <t>似乎是可以制作出一切的魔法道具</t>
   </si>
   <si>
     <t>addRandomCardIfNot(1,2,2)</t>
@@ -190,16 +226,19 @@
     <t>春来发枝</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 美化{added}，此牌美化的数值提升4</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  美化{added}，此牌美化的数值提升4</t>
   </si>
   <si>
     <t>addAddNum(4);magnify(0.2)</t>
   </si>
   <si>
-    <t>整冠截顶</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 拆卸{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
+    <t>轴承拉马</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
+  </si>
+  <si>
+    <t>一个小小的三爪工具，能把卡死在轴上的齿轮或轴承平稳拉出来。</t>
   </si>
   <si>
     <t>addNatureAtSumIf(40,1);shake(1,0.3)</t>
@@ -208,7 +247,7 @@
     <t>一叶知秋</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 将手牌中的所有礼物都变成同一个随机礼物</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  将手牌中的所有礼物都变成同一个随机礼物</t>
   </si>
   <si>
     <t>changeHandGift()</t>
@@ -217,7 +256,7 @@
     <t>提取</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;\n 从工具袋中取出2个物品</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  从工具袋中取出2个物品</t>
   </si>
   <si>
     <t>drawCard(2)</t>
@@ -226,7 +265,7 @@
     <t>移花接木</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 若卡组中有6个以上相同的礼物，美化所有相同的礼物80</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  若卡组中有6个以上相同的礼物，美化所有相同的礼物80</t>
   </si>
   <si>
     <t>addWIthSameTogether(6,80);magnify(0.5)</t>
@@ -235,7 +274,7 @@
     <t>抓取</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 从袋子里取出6个物品</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  从袋子里取出6个物品</t>
   </si>
   <si>
     <t>drawCard(6)</t>
@@ -244,13 +283,13 @@
     <t>大包装</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n  美化{added}</t>
-  </si>
-  <si>
-    <t>预支未来</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 下回合属性加成提升到2倍</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;   美化{added}</t>
+  </si>
+  <si>
+    <t>预知未来</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  下回合属性加成提升到2倍</t>
   </si>
   <si>
     <t>changeProperty(2)</t>
@@ -259,16 +298,7 @@
     <t>超级拼装</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 制造{made}</t>
-  </si>
-  <si>
-    <t>大盲盒</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;\n 随机获得3张罕见礼物牌</t>
-  </si>
-  <si>
-    <t>addRandomCard(1,2,3)</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  制造{made}</t>
   </si>
 </sst>
 </file>
@@ -940,26 +970,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1281,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12.4545454545455" style="2" customWidth="1"/>
@@ -1352,7 +1382,7 @@
       <c r="A2" s="3">
         <v>21601</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="3">
@@ -1367,7 +1397,7 @@
       <c r="F2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="7" t="s">
         <v>19</v>
       </c>
       <c r="H2">
@@ -1388,7 +1418,7 @@
         <v>10</v>
       </c>
       <c r="O2">
-        <f>N2*0.8</f>
+        <f t="shared" ref="O2:O8" si="0">N2*0.8</f>
         <v>8</v>
       </c>
       <c r="Q2">
@@ -1411,11 +1441,11 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
+      <c r="G3" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1430,13 +1460,13 @@
         <v>0</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N3">
         <v>20</v>
       </c>
       <c r="O3">
-        <f>N3*0.8</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="Q3">
@@ -1448,7 +1478,7 @@
         <v>21002</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1459,11 +1489,11 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
+      <c r="F4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1481,7 +1511,7 @@
         <v>20</v>
       </c>
       <c r="O4">
-        <f>N4*0.8</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="Q4">
@@ -1492,8 +1522,8 @@
       <c r="A5">
         <v>21003</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>25</v>
+      <c r="B5" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1504,11 +1534,11 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>19</v>
+      <c r="F5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -1523,13 +1553,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N5">
         <v>20</v>
       </c>
       <c r="O5">
-        <f>N5*0.8</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="Q5">
@@ -1541,7 +1571,7 @@
         <v>21004</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1552,11 +1582,11 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>29</v>
+      <c r="F6" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -1571,13 +1601,13 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <f>N6*0.8</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="Q6">
@@ -1589,7 +1619,7 @@
         <v>21005</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -1600,11 +1630,11 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>19</v>
+      <c r="F7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -1622,7 +1652,7 @@
         <v>20</v>
       </c>
       <c r="O7">
-        <f>N7*0.8</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="Q7">
@@ -1634,7 +1664,7 @@
         <v>21006</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1645,11 +1675,11 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>34</v>
+      <c r="F8" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H8">
         <v>3</v>
@@ -1664,13 +1694,13 @@
         <v>0</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N8">
         <v>20</v>
       </c>
       <c r="O8">
-        <f>N8*0.8</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="Q8">
@@ -1681,8 +1711,8 @@
       <c r="A9" s="9">
         <v>21007</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>36</v>
+      <c r="B9" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1693,14 +1723,14 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>37</v>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -1710,11 +1740,11 @@
       </c>
     </row>
     <row r="10" ht="27" customHeight="1" spans="1:17">
-      <c r="A10" s="10">
+      <c r="A10" s="11">
         <v>22001</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>39</v>
+      <c r="B10" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1725,11 +1755,11 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>40</v>
+      <c r="F10" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1747,7 +1777,7 @@
         <v>40</v>
       </c>
       <c r="O10">
-        <f t="shared" ref="O10:O17" si="0">N10*0.8</f>
+        <f t="shared" ref="O10:O23" si="1">N10*0.8</f>
         <v>32</v>
       </c>
       <c r="Q10">
@@ -1755,11 +1785,11 @@
       </c>
     </row>
     <row r="11" ht="51" customHeight="1" spans="1:17">
-      <c r="A11" s="10">
+      <c r="A11" s="11">
         <v>22002</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>41</v>
+      <c r="B11" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1770,11 +1800,11 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>42</v>
+      <c r="F11" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1789,13 +1819,13 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="N11">
         <v>40</v>
       </c>
       <c r="O11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="Q11">
@@ -1803,11 +1833,11 @@
       </c>
     </row>
     <row r="12" ht="27" customHeight="1" spans="1:17">
-      <c r="A12" s="10">
+      <c r="A12" s="11">
         <v>22003</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>70</v>
@@ -1818,14 +1848,14 @@
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>19</v>
+      <c r="F12" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1837,13 +1867,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N12">
         <v>40</v>
       </c>
       <c r="O12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="Q12">
@@ -1851,11 +1881,11 @@
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:17">
-      <c r="A13" s="10">
+      <c r="A13" s="11">
         <v>22004</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1866,14 +1896,14 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>19</v>
+      <c r="F13" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1885,13 +1915,13 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="N13">
         <v>40</v>
       </c>
       <c r="O13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="Q13">
@@ -1899,11 +1929,11 @@
       </c>
     </row>
     <row r="14" ht="29" customHeight="1" spans="1:17">
-      <c r="A14" s="10">
+      <c r="A14" s="11">
         <v>22005</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1914,11 +1944,11 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>50</v>
+      <c r="F14" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -1933,13 +1963,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="N14">
         <v>40</v>
       </c>
       <c r="O14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="Q14">
@@ -1947,11 +1977,11 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:17">
-      <c r="A15" s="10">
+      <c r="A15" s="11">
         <v>22006</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>52</v>
+      <c r="B15" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1962,14 +1992,14 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>53</v>
+      <c r="F15" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1981,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="N15">
         <v>40</v>
       </c>
       <c r="O15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="Q15">
@@ -1995,11 +2025,11 @@
       </c>
     </row>
     <row r="16" ht="56" spans="1:17">
-      <c r="A16" s="10">
+      <c r="A16" s="11">
         <v>22007</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2010,14 +2040,14 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>19</v>
+      <c r="F16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2029,13 +2059,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="N16">
         <v>40</v>
       </c>
       <c r="O16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="Q16">
@@ -2043,11 +2073,11 @@
       </c>
     </row>
     <row r="17" ht="33" customHeight="1" spans="1:17">
-      <c r="A17" s="10">
+      <c r="A17" s="11">
         <v>22008</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>58</v>
+      <c r="B17" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2058,11 +2088,11 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>59</v>
+      <c r="F17" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -2077,13 +2107,13 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="N17">
         <v>40</v>
       </c>
       <c r="O17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="Q17">
@@ -2091,11 +2121,11 @@
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="36" customHeight="1" spans="1:17">
-      <c r="A18" s="10">
+      <c r="A18" s="11">
         <v>22009</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>61</v>
+      <c r="B18" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -2107,20 +2137,20 @@
         <v>0</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H18"/>
       <c r="L18" s="14" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="N18" s="1">
         <v>80</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O24" si="1">N18*0.8</f>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="Q18">
@@ -2131,8 +2161,8 @@
       <c r="A19" s="1">
         <v>23001</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>64</v>
+      <c r="B19" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -2144,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H19">
         <v>4</v>
@@ -2162,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="N19" s="1">
         <v>80</v>
@@ -2180,7 +2210,7 @@
         <v>23002</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2192,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -2210,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="1">
@@ -2227,7 +2257,7 @@
         <v>23003</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2239,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H21">
         <v>3</v>
@@ -2263,7 +2293,7 @@
         <v>23004</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2275,13 +2305,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N22" s="1">
         <v>80</v>
@@ -2296,7 +2326,7 @@
         <v>23005</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2308,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -2323,39 +2353,6 @@
         <v>80</v>
       </c>
       <c r="O23">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" ht="42" spans="1:17">
-      <c r="A24" s="1">
-        <v>23006</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N24" s="1">
-        <v>80</v>
-      </c>
-      <c r="O24">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="88">
   <si>
     <t>id</t>
   </si>
@@ -85,7 +85,7 @@
     <t>漆笔</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 美化{added}</t>
+    <t>美化{added}</t>
   </si>
   <si>
     <t>绘制工具，可以让物品更美观</t>
@@ -94,7 +94,7 @@
     <t>DIY小屋零件切割板</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  制造{made}，也就是下回合获得你制造的牌</t>
+    <t>制造{made}，也就是下回合获得你制造的牌</t>
   </si>
   <si>
     <t>印有精确到毫米的网格和角度，板上的小木条再也不会切歪了。</t>
@@ -106,16 +106,13 @@
     <t>荧光夜光沙</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  美化{added}</t>
-  </si>
-  <si>
     <t>可以让处理后的物品闪闪发光</t>
   </si>
   <si>
     <t>撬片套装</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，本回合随机获得一张罕见礼物卡</t>
+    <t>拆卸{broken}，本回合随机获得一张罕见礼物卡</t>
   </si>
   <si>
     <t>塑料制成的各种薄片，可以用来撬动各种物品的外壳</t>
@@ -127,7 +124,7 @@
     <t>管钳扳手</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，蒂娜的属性三提升34点</t>
+    <t>拆卸{broken}，蒂娜的好感三提升34点</t>
   </si>
   <si>
     <t>形状奇特的扳手，更易于使用</t>
@@ -139,7 +136,7 @@
     <t>热风枪</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，蒂娜的的属性一提升{nature1}点</t>
+    <t>拆卸{broken}，蒂娜的的好感一提升{nature1}点</t>
   </si>
   <si>
     <t>能精准吹出高温气流，软化焊点或让不干胶标签完美撕下。</t>
@@ -148,7 +145,7 @@
     <t>马克笔</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  美化，将卡中数值不足14的部分加成到14</t>
+    <t>美化，将卡中数值不足14的部分加成到14</t>
   </si>
   <si>
     <t>绘制神器</t>
@@ -160,7 +157,7 @@
     <t>更新工具</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 制造{made}， 拆卸{broken}</t>
+    <t>制造{made}，拆卸{broken}</t>
   </si>
   <si>
     <t>卡牌介绍占坑</t>
@@ -172,7 +169,7 @@
     <t>热熔胶枪</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 制造{made}，下回合获得你制造的牌</t>
+    <t>制造{made}，下回合获得你制造的牌</t>
   </si>
   <si>
     <t>快速粘合小物件的神器</t>
@@ -181,7 +178,7 @@
     <t>金属冲压模具</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  制造{made}，本回合随机获得一张普通属性卡</t>
+    <t>制造{made}，本回合随机获得一张普通好感卡</t>
   </si>
   <si>
     <t>能把薄金属片压出花纹或字母，敲打的声音很有节奏感。</t>
@@ -193,7 +190,7 @@
     <t>精密镊子套装</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，蒂娜的属性一，属性三提升{nature1}点</t>
+    <t>拆卸{broken}，蒂娜的好感一，好感三提升{nature1}点</t>
   </si>
   <si>
     <t>弯头、直头、平口、尖嘴……拆解细微零件时绝不让它弹飞。</t>
@@ -202,7 +199,7 @@
     <t>彩色电化铝烫印箔</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  若卡组中有三个以上相同的礼物，美化40，否则美化6</t>
+    <t>若卡组中有三个以上相同的礼物，美化40，否则美化6</t>
   </si>
   <si>
     <t>用加热的铜章压一下，闪亮的镭射图案就会烙印上去</t>
@@ -214,7 +211,7 @@
     <t>凭空</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  若手中没有礼物牌，则随机获得两个罕见礼物卡</t>
+    <t>若手中没有礼物牌，则随机获得两个罕见礼物卡</t>
   </si>
   <si>
     <t>似乎是可以制作出一切的魔法道具</t>
@@ -226,7 +223,7 @@
     <t>春来发枝</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  美化{added}，此牌美化的数值提升4</t>
+    <t>美化{added}，此牌美化的数值提升4</t>
   </si>
   <si>
     <t>addAddNum(4);magnify(0.2)</t>
@@ -235,7 +232,7 @@
     <t>轴承拉马</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  拆卸{broken}，若此礼物包含属性一的加成，提升属性二40点</t>
+    <t>拆卸{broken}，若此礼物包含好感一的加成，提升好感二40点</t>
   </si>
   <si>
     <t>一个小小的三爪工具，能把卡死在轴上的齿轮或轴承平稳拉出来。</t>
@@ -247,7 +244,7 @@
     <t>一叶知秋</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  将手牌中的所有礼物都变成同一个随机礼物</t>
+    <t>将手牌中的所有礼物都变成同一个随机礼物</t>
   </si>
   <si>
     <t>changeHandGift()</t>
@@ -256,7 +253,7 @@
     <t>提取</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  从工具袋中取出2个物品</t>
+    <t>从书包中取出2个物品</t>
   </si>
   <si>
     <t>drawCard(2)</t>
@@ -265,7 +262,7 @@
     <t>移花接木</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  若卡组中有6个以上相同的礼物，美化所有相同的礼物80</t>
+    <t>若卡组中有6个以上相同的礼物，美化所有相同的礼物80</t>
   </si>
   <si>
     <t>addWIthSameTogether(6,80);magnify(0.5)</t>
@@ -274,7 +271,7 @@
     <t>抓取</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  从袋子里取出6个物品</t>
+    <t>从袋子里取出6个物品</t>
   </si>
   <si>
     <t>drawCard(6)</t>
@@ -283,13 +280,10 @@
     <t>大包装</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;   美化{added}</t>
-  </si>
-  <si>
     <t>预知未来</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  下回合属性加成提升到2倍</t>
+    <t>下回合好感加成提升到2倍</t>
   </si>
   <si>
     <t>changeProperty(2)</t>
@@ -298,7 +292,7 @@
     <t>超级拼装</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  制造{made}</t>
+    <t>制造{made}</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="28" spans="1:17">
+    <row r="2" ht="17.5" spans="1:17">
       <c r="A2" s="3">
         <v>21601</v>
       </c>
@@ -1425,7 +1419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="42" spans="1:17">
+    <row r="3" ht="28" spans="1:17">
       <c r="A3">
         <v>21001</v>
       </c>
@@ -1490,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1523,22 +1517,22 @@
         <v>21003</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -1553,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N5">
         <v>20</v>
@@ -1566,27 +1560,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="42" spans="1:17">
+    <row r="6" ht="28" spans="1:17">
       <c r="A6">
         <v>21004</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -1601,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N6">
         <v>20</v>
@@ -1614,12 +1608,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:17">
+    <row r="7" ht="28" spans="1:17">
       <c r="A7">
         <v>21005</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -1631,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -1664,22 +1658,22 @@
         <v>21006</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="H8">
         <v>3</v>
@@ -1694,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N8">
         <v>20</v>
@@ -1712,25 +1706,25 @@
         <v>21007</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" t="s">
         <v>44</v>
-      </c>
-      <c r="H9" t="s">
-        <v>45</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -1744,22 +1738,22 @@
         <v>22001</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1789,22 +1783,22 @@
         <v>22002</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1819,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N11">
         <v>40</v>
@@ -1837,7 +1831,7 @@
         <v>22003</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12">
         <v>70</v>
@@ -1849,10 +1843,10 @@
         <v>60</v>
       </c>
       <c r="F12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -1885,22 +1879,22 @@
         <v>22004</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="H13">
         <v>3</v>
@@ -1915,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N13">
         <v>40</v>
@@ -1933,22 +1927,22 @@
         <v>22005</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -1963,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N14">
         <v>40</v>
@@ -1981,22 +1975,22 @@
         <v>22006</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="G15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -2011,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N15">
         <v>40</v>
@@ -2024,27 +2018,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="56" spans="1:17">
+    <row r="16" ht="42" spans="1:17">
       <c r="A16" s="11">
         <v>22007</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -2059,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N16">
         <v>40</v>
@@ -2077,22 +2071,22 @@
         <v>22008</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="G17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -2107,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N17">
         <v>40</v>
@@ -2125,26 +2119,26 @@
         <v>22009</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="1">
-        <v>0</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H18"/>
       <c r="L18" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N18" s="1">
         <v>80</v>
@@ -2162,22 +2156,22 @@
         <v>23001</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>78</v>
-      </c>
       <c r="G19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H19">
         <v>4</v>
@@ -2192,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N19" s="1">
         <v>80</v>
@@ -2210,22 +2204,22 @@
         <v>23002</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>81</v>
-      </c>
       <c r="G20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -2240,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="1">
@@ -2252,12 +2246,12 @@
       </c>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" ht="28" spans="1:17">
+    <row r="21" spans="1:17">
       <c r="A21" s="1">
         <v>23003</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2269,10 +2263,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H21">
         <v>3</v>
@@ -2288,30 +2282,30 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" ht="42" spans="1:17">
+    <row r="22" ht="28" spans="1:17">
       <c r="A22" s="1">
         <v>23004</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="N22" s="1">
         <v>80</v>
@@ -2321,12 +2315,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" ht="28" spans="1:17">
+    <row r="23" spans="1:17">
       <c r="A23" s="1">
         <v>23005</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2338,10 +2332,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H23">
         <v>1</v>

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -82,13 +82,13 @@
     <t>dialog</t>
   </si>
   <si>
-    <t>漆笔</t>
+    <t>企鹅创口贴</t>
   </si>
   <si>
     <t>美化{added}</t>
   </si>
   <si>
-    <t>绘制工具，可以让物品更美观</t>
+    <t>印有企鹅图案的创口贴，深受自闭症人士喜欢，可以让物品更美观</t>
   </si>
   <si>
     <t>DIY小屋零件切割板</t>
@@ -316,13 +316,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF0F1115"/>
-      <name val="宋体"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -976,13 +976,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1372,7 +1372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="17.5" spans="1:17">
+    <row r="2" ht="15" spans="1:17">
       <c r="A2" s="3">
         <v>21601</v>
       </c>
@@ -1391,7 +1391,7 @@
       <c r="F2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="H2">
@@ -1423,7 +1423,7 @@
       <c r="A3">
         <v>21001</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C3">
@@ -1438,7 +1438,7 @@
       <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
       <c r="H3">
@@ -1471,7 +1471,7 @@
       <c r="A4">
         <v>21002</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C4">
@@ -1486,7 +1486,7 @@
       <c r="F4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H4">
@@ -1516,7 +1516,7 @@
       <c r="A5">
         <v>21003</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C5">
@@ -1531,7 +1531,7 @@
       <c r="F5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="H5">
@@ -1564,7 +1564,7 @@
       <c r="A6">
         <v>21004</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C6">
@@ -1612,7 +1612,7 @@
       <c r="A7">
         <v>21005</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C7">
@@ -1627,7 +1627,7 @@
       <c r="F7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="H7">
@@ -1657,7 +1657,7 @@
       <c r="A8">
         <v>21006</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C8">
@@ -1830,7 +1830,7 @@
       <c r="A12" s="11">
         <v>22003</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C12">
@@ -1845,7 +1845,7 @@
       <c r="F12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>54</v>
       </c>
       <c r="H12">
@@ -1878,7 +1878,7 @@
       <c r="A13" s="11">
         <v>22004</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>55</v>
       </c>
       <c r="C13">
@@ -1893,7 +1893,7 @@
       <c r="F13" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>57</v>
       </c>
       <c r="H13">
@@ -2022,7 +2022,7 @@
       <c r="A16" s="11">
         <v>22007</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>66</v>
       </c>
       <c r="C16">
@@ -2037,7 +2037,7 @@
       <c r="F16" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="7" t="s">
         <v>68</v>
       </c>
       <c r="H16">
@@ -2070,7 +2070,7 @@
       <c r="A17" s="11">
         <v>22008</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C17">
@@ -2118,7 +2118,7 @@
       <c r="A18" s="11">
         <v>22009</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C18" s="1">
@@ -2155,7 +2155,7 @@
       <c r="A19" s="1">
         <v>23001</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>76</v>
       </c>
       <c r="C19" s="1">

--- a/funcCard.xlsx
+++ b/funcCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -91,22 +91,22 @@
     <t>印有企鹅图案的创口贴，深受自闭症人士喜欢，可以让物品更美观</t>
   </si>
   <si>
-    <t>DIY小屋零件切割板</t>
+    <t>切割板</t>
   </si>
   <si>
     <t>制造{made}，也就是下回合获得你制造的牌</t>
   </si>
   <si>
-    <t>印有精确到毫米的网格和角度，板上的小木条再也不会切歪了。</t>
+    <t>印有精确到毫米的网格和角度，再也不会切歪物品了。</t>
   </si>
   <si>
     <t>shake(1,0.2)</t>
   </si>
   <si>
-    <t>荧光夜光沙</t>
-  </si>
-  <si>
-    <t>可以让处理后的物品闪闪发光</t>
+    <t>贴纸</t>
+  </si>
+  <si>
+    <t>可以随意地贴在物品上</t>
   </si>
   <si>
     <t>撬片套装</t>
@@ -160,70 +160,73 @@
     <t>制造{made}，拆卸{broken}</t>
   </si>
   <si>
+    <t>趁手的生产工具，但需要牺牲一点物品</t>
+  </si>
+  <si>
+    <t>1,2,6</t>
+  </si>
+  <si>
+    <t>热熔胶枪</t>
+  </si>
+  <si>
+    <t>制造{made}，下回合获得你制造的牌</t>
+  </si>
+  <si>
+    <t>快速粘合小物件的神器</t>
+  </si>
+  <si>
+    <t>冲压模具</t>
+  </si>
+  <si>
+    <t>制造{made}，本回合随机获得一张普通好感卡</t>
+  </si>
+  <si>
+    <t>能把薄金属片压出花纹或字母，敲打的声音很有节奏感。</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,1,1);shake(1,0.2)</t>
+  </si>
+  <si>
+    <t>镊子套装</t>
+  </si>
+  <si>
+    <t>拆卸{broken}，蒂娜的好感一，好感三提升{nature1}点</t>
+  </si>
+  <si>
+    <t>弯头、直头、平口、尖嘴……拆解细微零件时绝不让它弹飞。</t>
+  </si>
+  <si>
+    <t>丝带</t>
+  </si>
+  <si>
+    <t>若卡组中有三个以上相同的礼物，美化40，否则美化6</t>
+  </si>
+  <si>
+    <t>打包装好的礼物，可以让其更加美观</t>
+  </si>
+  <si>
+    <t>addWithSame(3,40,5);magnify(0.3)</t>
+  </si>
+  <si>
+    <t>骨刀</t>
+  </si>
+  <si>
+    <t>若手中没有礼物牌，则随机获得两个罕见礼物卡</t>
+  </si>
+  <si>
+    <t>似乎是可以制作出一切的魔法道具</t>
+  </si>
+  <si>
+    <t>addRandomCardIfNot(1,2,2)</t>
+  </si>
+  <si>
+    <t>春来发枝</t>
+  </si>
+  <si>
+    <t>美化{added}，此牌美化的数值提升4</t>
+  </si>
+  <si>
     <t>卡牌介绍占坑</t>
-  </si>
-  <si>
-    <t>1,2,6</t>
-  </si>
-  <si>
-    <t>热熔胶枪</t>
-  </si>
-  <si>
-    <t>制造{made}，下回合获得你制造的牌</t>
-  </si>
-  <si>
-    <t>快速粘合小物件的神器</t>
-  </si>
-  <si>
-    <t>金属冲压模具</t>
-  </si>
-  <si>
-    <t>制造{made}，本回合随机获得一张普通好感卡</t>
-  </si>
-  <si>
-    <t>能把薄金属片压出花纹或字母，敲打的声音很有节奏感。</t>
-  </si>
-  <si>
-    <t>addRandomCard(1,1,1);shake(1,0.2)</t>
-  </si>
-  <si>
-    <t>精密镊子套装</t>
-  </si>
-  <si>
-    <t>拆卸{broken}，蒂娜的好感一，好感三提升{nature1}点</t>
-  </si>
-  <si>
-    <t>弯头、直头、平口、尖嘴……拆解细微零件时绝不让它弹飞。</t>
-  </si>
-  <si>
-    <t>彩色电化铝烫印箔</t>
-  </si>
-  <si>
-    <t>若卡组中有三个以上相同的礼物，美化40，否则美化6</t>
-  </si>
-  <si>
-    <t>用加热的铜章压一下，闪亮的镭射图案就会烙印上去</t>
-  </si>
-  <si>
-    <t>addWithSame(3,40,5);magnify(0.3)</t>
-  </si>
-  <si>
-    <t>凭空</t>
-  </si>
-  <si>
-    <t>若手中没有礼物牌，则随机获得两个罕见礼物卡</t>
-  </si>
-  <si>
-    <t>似乎是可以制作出一切的魔法道具</t>
-  </si>
-  <si>
-    <t>addRandomCardIfNot(1,2,2)</t>
-  </si>
-  <si>
-    <t>春来发枝</t>
-  </si>
-  <si>
-    <t>美化{added}，此牌美化的数值提升4</t>
   </si>
   <si>
     <t>addAddNum(4);magnify(0.2)</t>
@@ -305,7 +308,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,6 +326,12 @@
       <sz val="12"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -815,137 +824,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -967,12 +976,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -985,13 +994,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1423,7 +1438,7 @@
       <c r="A3">
         <v>21001</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C3">
@@ -1435,10 +1450,10 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H3">
@@ -1471,7 +1486,7 @@
       <c r="A4">
         <v>21002</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C4">
@@ -1483,7 +1498,7 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -1516,7 +1531,7 @@
       <c r="A5">
         <v>21003</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C5">
@@ -1528,7 +1543,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -1564,7 +1579,7 @@
       <c r="A6">
         <v>21004</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C6">
@@ -1576,7 +1591,7 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -1612,7 +1627,7 @@
       <c r="A7">
         <v>21005</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C7">
@@ -1624,10 +1639,10 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>36</v>
       </c>
       <c r="H7">
@@ -1657,7 +1672,7 @@
       <c r="A8">
         <v>21006</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C8">
@@ -1669,7 +1684,7 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -1717,7 +1732,7 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -1731,6 +1746,13 @@
       </c>
       <c r="J9">
         <v>1</v>
+      </c>
+      <c r="N9">
+        <v>20</v>
+      </c>
+      <c r="O9">
+        <f>N9*0.8</f>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1" spans="1:17">
@@ -1749,7 +1771,7 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>46</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -1782,7 +1804,7 @@
       <c r="A11" s="11">
         <v>22002</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>48</v>
       </c>
       <c r="C11">
@@ -1794,7 +1816,7 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -1830,7 +1852,7 @@
       <c r="A12" s="11">
         <v>22003</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C12">
@@ -1842,10 +1864,10 @@
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>54</v>
       </c>
       <c r="H12">
@@ -1878,7 +1900,7 @@
       <c r="A13" s="11">
         <v>22004</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C13">
@@ -1890,7 +1912,7 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>56</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -1926,7 +1948,7 @@
       <c r="A14" s="11">
         <v>22005</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="13" t="s">
         <v>59</v>
       </c>
       <c r="C14">
@@ -1938,7 +1960,7 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -1986,11 +2008,11 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>43</v>
+      <c r="G15" s="14" t="s">
+        <v>65</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -2005,7 +2027,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N15">
         <v>40</v>
@@ -2022,8 +2044,8 @@
       <c r="A16" s="11">
         <v>22007</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>66</v>
+      <c r="B16" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2034,11 +2056,11 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>68</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -2053,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N16">
         <v>40</v>
@@ -2070,8 +2092,8 @@
       <c r="A17" s="11">
         <v>22008</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>70</v>
+      <c r="B17" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2082,11 +2104,11 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>71</v>
+      <c r="F17" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -2101,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N17">
         <v>40</v>
@@ -2119,7 +2141,7 @@
         <v>22009</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -2130,15 +2152,15 @@
       <c r="E18" s="1">
         <v>0</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>74</v>
+      <c r="F18" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H18"/>
-      <c r="L18" s="14" t="s">
-        <v>75</v>
+      <c r="L18" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="N18" s="1">
         <v>80</v>
@@ -2155,8 +2177,8 @@
       <c r="A19" s="1">
         <v>23001</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>76</v>
+      <c r="B19" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -2167,11 +2189,11 @@
       <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>77</v>
+      <c r="F19" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H19">
         <v>4</v>
@@ -2185,8 +2207,8 @@
       <c r="K19" s="1">
         <v>0</v>
       </c>
-      <c r="L19" s="14" t="s">
-        <v>78</v>
+      <c r="L19" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="N19" s="1">
         <v>80</v>
@@ -2204,7 +2226,7 @@
         <v>23002</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2215,11 +2237,11 @@
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>80</v>
+      <c r="F20" s="17" t="s">
+        <v>81</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -2234,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="1">
@@ -2251,7 +2273,7 @@
         <v>23003</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2266,7 +2288,7 @@
         <v>18</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H21">
         <v>3</v>
@@ -2287,7 +2309,7 @@
         <v>23004</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2299,13 +2321,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N22" s="1">
         <v>80</v>
@@ -2320,7 +2342,7 @@
         <v>23005</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2332,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H23">
         <v>1</v>
